--- a/experiment/instructions/ai_query_11_classified.xlsx
+++ b/experiment/instructions/ai_query_11_classified.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/elfre4573/Library/CloudStorage/Dropbox/Research projects/AI advice/experiment/instructions/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/elfre4573/Documents/GitHub/AI_advice/experiment/instructions/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49744AF6-5BCB-FE42-9CD7-60706F136E00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0BDF674-1AB9-1243-88B0-9D62C319BCB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33560" yWindow="-1360" windowWidth="30240" windowHeight="17480" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17480" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="give 3" sheetId="2" r:id="rId1"/>
@@ -19,6 +19,10 @@
     <sheet name="take 4" sheetId="4" r:id="rId4"/>
     <sheet name="others" sheetId="3" r:id="rId5"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'give 0'!$A$1:$D$159</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'give 3 - full sentence'!$A$1:$D$96</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
@@ -3168,26 +3172,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -3227,7 +3224,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="3">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3252,38 +3249,6 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -3589,605 +3554,605 @@
   <dimension ref="A1:J96"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="54.5" style="6" customWidth="1"/>
-    <col min="3" max="3" width="54.1640625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="54.1640625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="54.5" style="2" customWidth="1"/>
+    <col min="3" max="3" width="54.1640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="54.1640625" style="2" customWidth="1"/>
     <col min="7" max="7" width="54.5" customWidth="1"/>
-    <col min="10" max="10" width="44" style="3" customWidth="1"/>
+    <col min="10" max="10" width="44" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="5" t="s">
         <v>794</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="5" t="s">
         <v>320</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="5" t="s">
         <v>321</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="5" t="s">
         <v>323</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="5" t="s">
         <v>322</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="144" x14ac:dyDescent="0.2">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="7" t="s">
         <v>309</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="J2" s="4" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="112" x14ac:dyDescent="0.2">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="4" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="144" x14ac:dyDescent="0.2">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>296</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="J4" s="4" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="128" x14ac:dyDescent="0.2">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="4" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="128" x14ac:dyDescent="0.2">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="4" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="144" x14ac:dyDescent="0.2">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="4" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="128" x14ac:dyDescent="0.2">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="5"/>
+      <c r="G8" s="4"/>
     </row>
     <row r="9" spans="1:10" ht="128" x14ac:dyDescent="0.2">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="144" x14ac:dyDescent="0.2">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="128" x14ac:dyDescent="0.2">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="128" x14ac:dyDescent="0.2">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="144" x14ac:dyDescent="0.2">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="4" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="112" x14ac:dyDescent="0.2">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="4" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="128" x14ac:dyDescent="0.2">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="4" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="112" x14ac:dyDescent="0.2">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="4" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="112" x14ac:dyDescent="0.2">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="4" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="128" x14ac:dyDescent="0.2">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="4" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="128" x14ac:dyDescent="0.2">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="4" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="144" x14ac:dyDescent="0.2">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="4" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="128" x14ac:dyDescent="0.2">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="4" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="128" x14ac:dyDescent="0.2">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="4" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="128" x14ac:dyDescent="0.2">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="4" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="128" x14ac:dyDescent="0.2">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="4" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="128" x14ac:dyDescent="0.2">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="4" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="96" x14ac:dyDescent="0.2">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="4" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="112" x14ac:dyDescent="0.2">
-      <c r="A27" s="5" t="s">
+      <c r="A27" s="4" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="128" x14ac:dyDescent="0.2">
-      <c r="A28" s="5" t="s">
+      <c r="A28" s="4" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="112" x14ac:dyDescent="0.2">
-      <c r="A29" s="5" t="s">
+      <c r="A29" s="4" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="128" x14ac:dyDescent="0.2">
-      <c r="A30" s="5" t="s">
+      <c r="A30" s="4" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="128" x14ac:dyDescent="0.2">
-      <c r="A31" s="5" t="s">
+      <c r="A31" s="4" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="144" x14ac:dyDescent="0.2">
-      <c r="A32" s="5" t="s">
+      <c r="A32" s="4" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="128" x14ac:dyDescent="0.2">
-      <c r="A33" s="5" t="s">
+      <c r="A33" s="4" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="34" spans="1:1" ht="128" x14ac:dyDescent="0.2">
-      <c r="A34" s="5" t="s">
+      <c r="A34" s="4" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="35" spans="1:1" ht="128" x14ac:dyDescent="0.2">
-      <c r="A35" s="5" t="s">
+      <c r="A35" s="4" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="36" spans="1:1" ht="144" x14ac:dyDescent="0.2">
-      <c r="A36" s="5" t="s">
+      <c r="A36" s="4" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="37" spans="1:1" ht="128" x14ac:dyDescent="0.2">
-      <c r="A37" s="5" t="s">
+      <c r="A37" s="4" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="38" spans="1:1" ht="128" x14ac:dyDescent="0.2">
-      <c r="A38" s="5" t="s">
+      <c r="A38" s="4" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="39" spans="1:1" ht="128" x14ac:dyDescent="0.2">
-      <c r="A39" s="5" t="s">
+      <c r="A39" s="4" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="40" spans="1:1" ht="128" x14ac:dyDescent="0.2">
-      <c r="A40" s="5" t="s">
+      <c r="A40" s="4" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="41" spans="1:1" ht="128" x14ac:dyDescent="0.2">
-      <c r="A41" s="5" t="s">
+      <c r="A41" s="4" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="42" spans="1:1" ht="128" x14ac:dyDescent="0.2">
-      <c r="A42" s="5" t="s">
+      <c r="A42" s="4" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="43" spans="1:1" ht="128" x14ac:dyDescent="0.2">
-      <c r="A43" s="5" t="s">
+      <c r="A43" s="4" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="44" spans="1:1" ht="96" x14ac:dyDescent="0.2">
-      <c r="A44" s="5" t="s">
+      <c r="A44" s="4" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="45" spans="1:1" ht="128" x14ac:dyDescent="0.2">
-      <c r="A45" s="5" t="s">
+      <c r="A45" s="4" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="46" spans="1:1" ht="128" x14ac:dyDescent="0.2">
-      <c r="A46" s="5" t="s">
+      <c r="A46" s="4" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="47" spans="1:1" ht="96" x14ac:dyDescent="0.2">
-      <c r="A47" s="5" t="s">
+      <c r="A47" s="4" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="48" spans="1:1" ht="144" x14ac:dyDescent="0.2">
-      <c r="A48" s="5" t="s">
+      <c r="A48" s="4" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="49" spans="1:1" ht="128" x14ac:dyDescent="0.2">
-      <c r="A49" s="5" t="s">
+      <c r="A49" s="4" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="50" spans="1:1" ht="128" x14ac:dyDescent="0.2">
-      <c r="A50" s="5" t="s">
+      <c r="A50" s="4" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="51" spans="1:1" ht="128" x14ac:dyDescent="0.2">
-      <c r="A51" s="5" t="s">
+      <c r="A51" s="4" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="52" spans="1:1" ht="128" x14ac:dyDescent="0.2">
-      <c r="A52" s="5" t="s">
+      <c r="A52" s="4" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="53" spans="1:1" ht="128" x14ac:dyDescent="0.2">
-      <c r="A53" s="5" t="s">
+      <c r="A53" s="4" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="54" spans="1:1" ht="128" x14ac:dyDescent="0.2">
-      <c r="A54" s="5" t="s">
+      <c r="A54" s="4" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="55" spans="1:1" ht="128" x14ac:dyDescent="0.2">
-      <c r="A55" s="5" t="s">
+      <c r="A55" s="4" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="56" spans="1:1" ht="128" x14ac:dyDescent="0.2">
-      <c r="A56" s="5" t="s">
+      <c r="A56" s="4" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="57" spans="1:1" ht="144" x14ac:dyDescent="0.2">
-      <c r="A57" s="5" t="s">
+      <c r="A57" s="4" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="58" spans="1:1" ht="80" x14ac:dyDescent="0.2">
-      <c r="A58" s="5" t="s">
+      <c r="A58" s="4" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="59" spans="1:1" ht="128" x14ac:dyDescent="0.2">
-      <c r="A59" s="5" t="s">
+      <c r="A59" s="4" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="60" spans="1:1" ht="128" x14ac:dyDescent="0.2">
-      <c r="A60" s="5" t="s">
+      <c r="A60" s="4" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="61" spans="1:1" ht="128" x14ac:dyDescent="0.2">
-      <c r="A61" s="5" t="s">
+      <c r="A61" s="4" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="62" spans="1:1" ht="112" x14ac:dyDescent="0.2">
-      <c r="A62" s="5" t="s">
+      <c r="A62" s="4" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="63" spans="1:1" ht="96" x14ac:dyDescent="0.2">
-      <c r="A63" s="5" t="s">
+      <c r="A63" s="4" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="64" spans="1:1" ht="128" x14ac:dyDescent="0.2">
-      <c r="A64" s="5" t="s">
+      <c r="A64" s="4" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="65" spans="1:1" ht="128" x14ac:dyDescent="0.2">
-      <c r="A65" s="5" t="s">
+      <c r="A65" s="4" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="66" spans="1:1" ht="144" x14ac:dyDescent="0.2">
-      <c r="A66" s="5" t="s">
+      <c r="A66" s="4" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="67" spans="1:1" ht="144" x14ac:dyDescent="0.2">
-      <c r="A67" s="5" t="s">
+      <c r="A67" s="4" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="68" spans="1:1" ht="128" x14ac:dyDescent="0.2">
-      <c r="A68" s="5" t="s">
+      <c r="A68" s="4" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="69" spans="1:1" ht="128" x14ac:dyDescent="0.2">
-      <c r="A69" s="5" t="s">
+      <c r="A69" s="4" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="70" spans="1:1" ht="128" x14ac:dyDescent="0.2">
-      <c r="A70" s="5" t="s">
+      <c r="A70" s="4" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="71" spans="1:1" ht="128" x14ac:dyDescent="0.2">
-      <c r="A71" s="5" t="s">
+      <c r="A71" s="4" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="72" spans="1:1" ht="96" x14ac:dyDescent="0.2">
-      <c r="A72" s="5" t="s">
+      <c r="A72" s="4" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="73" spans="1:1" ht="112" x14ac:dyDescent="0.2">
-      <c r="A73" s="5" t="s">
+      <c r="A73" s="4" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="74" spans="1:1" ht="128" x14ac:dyDescent="0.2">
-      <c r="A74" s="5" t="s">
+      <c r="A74" s="4" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="75" spans="1:1" ht="128" x14ac:dyDescent="0.2">
-      <c r="A75" s="5" t="s">
+      <c r="A75" s="4" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="76" spans="1:1" ht="128" x14ac:dyDescent="0.2">
-      <c r="A76" s="5" t="s">
+      <c r="A76" s="4" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="77" spans="1:1" ht="112" x14ac:dyDescent="0.2">
-      <c r="A77" s="5" t="s">
+      <c r="A77" s="4" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="78" spans="1:1" ht="128" x14ac:dyDescent="0.2">
-      <c r="A78" s="5" t="s">
+      <c r="A78" s="4" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="79" spans="1:1" ht="128" x14ac:dyDescent="0.2">
-      <c r="A79" s="5" t="s">
+      <c r="A79" s="4" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="80" spans="1:1" ht="128" x14ac:dyDescent="0.2">
-      <c r="A80" s="5" t="s">
+      <c r="A80" s="4" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="81" spans="1:1" ht="128" x14ac:dyDescent="0.2">
-      <c r="A81" s="5" t="s">
+      <c r="A81" s="4" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="82" spans="1:1" ht="80" x14ac:dyDescent="0.2">
-      <c r="A82" s="5" t="s">
+      <c r="A82" s="4" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="83" spans="1:1" ht="128" x14ac:dyDescent="0.2">
-      <c r="A83" s="5" t="s">
+      <c r="A83" s="4" t="s">
         <v>304</v>
       </c>
     </row>
     <row r="84" spans="1:1" ht="96" x14ac:dyDescent="0.2">
-      <c r="A84" s="5" t="s">
+      <c r="A84" s="4" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="85" spans="1:1" ht="112" x14ac:dyDescent="0.2">
-      <c r="A85" s="5" t="s">
+      <c r="A85" s="4" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="86" spans="1:1" ht="112" x14ac:dyDescent="0.2">
-      <c r="A86" s="5" t="s">
+      <c r="A86" s="4" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="87" spans="1:1" ht="128" x14ac:dyDescent="0.2">
-      <c r="A87" s="5" t="s">
+      <c r="A87" s="4" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="88" spans="1:1" ht="128" x14ac:dyDescent="0.2">
-      <c r="A88" s="5" t="s">
+      <c r="A88" s="4" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="89" spans="1:1" ht="128" x14ac:dyDescent="0.2">
-      <c r="A89" s="5" t="s">
+      <c r="A89" s="4" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="90" spans="1:1" ht="128" x14ac:dyDescent="0.2">
-      <c r="A90" s="5" t="s">
+      <c r="A90" s="4" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="91" spans="1:1" ht="128" x14ac:dyDescent="0.2">
-      <c r="A91" s="5" t="s">
+      <c r="A91" s="4" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="92" spans="1:1" ht="112" x14ac:dyDescent="0.2">
-      <c r="A92" s="5" t="s">
+      <c r="A92" s="4" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="93" spans="1:1" ht="112" x14ac:dyDescent="0.2">
-      <c r="A93" s="5" t="s">
+      <c r="A93" s="4" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="94" spans="1:1" ht="112" x14ac:dyDescent="0.2">
-      <c r="A94" s="5" t="s">
+      <c r="A94" s="4" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="95" spans="1:1" ht="112" x14ac:dyDescent="0.2">
-      <c r="A95" s="5" t="s">
+      <c r="A95" s="4" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="96" spans="1:1" ht="112" x14ac:dyDescent="0.2">
-      <c r="A96" s="5" t="s">
+      <c r="A96" s="4" t="s">
         <v>30</v>
       </c>
     </row>
@@ -4195,12 +4160,12 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C2:C24">
     <sortCondition sortBy="cellColor" ref="C2:C24" dxfId="2"/>
   </sortState>
-  <conditionalFormatting sqref="G8 J2:J4 C2:C24 A96 G2 E2:E8">
+  <conditionalFormatting sqref="G2 J2:J4 E2:E8 C2:C24 G8 A96">
     <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="The decision-maker should give $3 to the recipient">
       <formula>NOT(ISERROR(SEARCH("The decision-maker should give $3 to the recipient",A2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C31:C1048576 G8 J2:J4 C2:C24 A96 G2 E2:E8">
+  <conditionalFormatting sqref="G2 J2:J4 E2:E8 C2:C24 G8 C31:C1048576 A96">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="The decision maker should give $3 to the recipient">
       <formula>NOT(ISERROR(SEARCH("The decision maker should give $3 to the recipient",A2)))</formula>
     </cfRule>
@@ -4211,3582 +4176,3636 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9507E3AC-07A7-7A43-825A-CB56AF56021E}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:D96"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="32.83203125" style="3" customWidth="1"/>
-    <col min="2" max="2" width="40.83203125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="42" style="3" customWidth="1"/>
-    <col min="4" max="4" width="44" style="3" customWidth="1"/>
+    <col min="1" max="1" width="32.83203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="40.83203125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="42" style="2" customWidth="1"/>
+    <col min="4" max="4" width="44" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="15" t="s">
         <v>327</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="15" t="s">
         <v>328</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="15" t="s">
         <v>329</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="15" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A2" s="12" t="s">
+    <row r="2" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="9" t="s">
         <v>643</v>
       </c>
-      <c r="B2" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C2" s="12" t="s">
+      <c r="B2" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C2" s="9" t="s">
         <v>645</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="9" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="9" t="s">
         <v>646</v>
       </c>
-      <c r="B3" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C3" s="12" t="s">
+      <c r="B3" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C3" s="9" t="s">
         <v>647</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="9" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="9" t="s">
         <v>648</v>
       </c>
-      <c r="B4" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C4" s="12" t="s">
+      <c r="B4" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C4" s="9" t="s">
         <v>649</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="9" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="84" x14ac:dyDescent="0.2">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="9" t="s">
         <v>650</v>
       </c>
-      <c r="B5" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C5" s="12" t="s">
+      <c r="B5" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C5" s="9" t="s">
         <v>651</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="9" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="9" t="s">
         <v>650</v>
       </c>
-      <c r="B6" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C6" s="12" t="s">
+      <c r="B6" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C6" s="9" t="s">
         <v>652</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="9" t="s">
         <v>304</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="9" t="s">
         <v>653</v>
       </c>
-      <c r="B7" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C7" s="12" t="s">
+      <c r="B7" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C7" s="9" t="s">
         <v>654</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="9" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="140" x14ac:dyDescent="0.2">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="9" t="s">
         <v>655</v>
       </c>
-      <c r="B8" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C8" s="12" t="s">
+      <c r="B8" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C8" s="9" t="s">
         <v>656</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="9" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="140" x14ac:dyDescent="0.2">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="9" t="s">
         <v>657</v>
       </c>
-      <c r="B9" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C9" s="12" t="s">
+      <c r="B9" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C9" s="9" t="s">
         <v>658</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="9" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="112" x14ac:dyDescent="0.2">
-      <c r="A10" s="19" t="s">
+    <row r="10" spans="1:4" ht="112" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="10" t="s">
+        <v>787</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>788</v>
+      </c>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="112" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="16" t="s">
         <v>659</v>
       </c>
-      <c r="B10" s="19" t="s">
-        <v>644</v>
-      </c>
-      <c r="C10" s="19" t="s">
+      <c r="B11" s="16" t="s">
+        <v>644</v>
+      </c>
+      <c r="C11" s="16" t="s">
         <v>660</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="D11" s="16" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A11" s="12" t="s">
+    <row r="12" spans="1:4" ht="112" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="10" t="s">
+        <v>775</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>776</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>777</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="112" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="10" t="s">
+        <v>775</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>792</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>793</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="9" t="s">
         <v>661</v>
       </c>
-      <c r="B11" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C11" s="12" t="s">
+      <c r="B14" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C14" s="9" t="s">
         <v>662</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="D14" s="9" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="112" x14ac:dyDescent="0.2">
-      <c r="A12" s="12" t="s">
+    <row r="15" spans="1:4" ht="112" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="9" t="s">
+        <v>666</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>667</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="112" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="9" t="s">
         <v>663</v>
       </c>
-      <c r="B12" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C12" s="12" t="s">
+      <c r="B16" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C16" s="9" t="s">
         <v>664</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D16" s="9" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A13" s="19" t="s">
+    <row r="17" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="16" t="s">
         <v>663</v>
       </c>
-      <c r="B13" s="19" t="s">
-        <v>644</v>
-      </c>
-      <c r="C13" s="19" t="s">
+      <c r="B17" s="16" t="s">
+        <v>644</v>
+      </c>
+      <c r="C17" s="16" t="s">
         <v>665</v>
       </c>
-      <c r="D13" s="19" t="s">
+      <c r="D17" s="16" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="112" x14ac:dyDescent="0.2">
-      <c r="A14" s="12" t="s">
-        <v>666</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>667</v>
-      </c>
-      <c r="D14" s="12" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A15" s="12" t="s">
+    <row r="18" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="9" t="s">
         <v>668</v>
       </c>
-      <c r="B15" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C15" s="12" t="s">
+      <c r="B18" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C18" s="9" t="s">
         <v>669</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D18" s="9" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="112" x14ac:dyDescent="0.2">
-      <c r="A16" s="12" t="s">
+    <row r="19" spans="1:4" ht="112" x14ac:dyDescent="0.2">
+      <c r="A19" s="9" t="s">
         <v>670</v>
       </c>
-      <c r="B16" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C16" s="12" t="s">
+      <c r="B19" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C19" s="9" t="s">
         <v>671</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D19" s="9" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A17" s="12" t="s">
+    <row r="20" spans="1:4" ht="126" x14ac:dyDescent="0.2">
+      <c r="A20" s="9" t="s">
         <v>672</v>
       </c>
-      <c r="B17" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C17" s="12" t="s">
+      <c r="B20" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C20" s="9" t="s">
         <v>673</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D20" s="9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A18" s="12" t="s">
+    <row r="21" spans="1:4" ht="126" x14ac:dyDescent="0.2">
+      <c r="A21" s="9" t="s">
         <v>672</v>
       </c>
-      <c r="B18" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C18" s="12" t="s">
+      <c r="B21" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C21" s="9" t="s">
         <v>674</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D21" s="9" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A19" s="12" t="s">
+    <row r="22" spans="1:4" ht="126" x14ac:dyDescent="0.2">
+      <c r="A22" s="9" t="s">
         <v>672</v>
       </c>
-      <c r="B19" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C19" s="12" t="s">
+      <c r="B22" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C22" s="9" t="s">
         <v>675</v>
       </c>
-      <c r="D19" s="12" t="s">
+      <c r="D22" s="9" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="84" x14ac:dyDescent="0.2">
-      <c r="A20" s="12" t="s">
+    <row r="23" spans="1:4" ht="84" x14ac:dyDescent="0.2">
+      <c r="A23" s="9" t="s">
         <v>672</v>
       </c>
-      <c r="B20" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C20" s="12" t="s">
+      <c r="B23" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C23" s="9" t="s">
         <v>676</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="D23" s="9" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A21" s="12" t="s">
+    <row r="24" spans="1:4" ht="126" x14ac:dyDescent="0.2">
+      <c r="A24" s="9" t="s">
         <v>672</v>
       </c>
-      <c r="B21" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C21" s="12" t="s">
+      <c r="B24" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C24" s="9" t="s">
         <v>677</v>
       </c>
-      <c r="D21" s="12" t="s">
+      <c r="D24" s="9" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="112" x14ac:dyDescent="0.2">
-      <c r="A22" s="12" t="s">
+    <row r="25" spans="1:4" ht="112" x14ac:dyDescent="0.2">
+      <c r="A25" s="9" t="s">
         <v>672</v>
       </c>
-      <c r="B22" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C22" s="12" t="s">
+      <c r="B25" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C25" s="9" t="s">
         <v>678</v>
       </c>
-      <c r="D22" s="12" t="s">
+      <c r="D25" s="9" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A23" s="12" t="s">
+    <row r="26" spans="1:4" ht="126" x14ac:dyDescent="0.2">
+      <c r="A26" s="9" t="s">
         <v>672</v>
       </c>
-      <c r="B23" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C23" s="12" t="s">
+      <c r="B26" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C26" s="9" t="s">
         <v>679</v>
       </c>
-      <c r="D23" s="12" t="s">
+      <c r="D26" s="9" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="112" x14ac:dyDescent="0.2">
-      <c r="A24" s="12" t="s">
+    <row r="27" spans="1:4" ht="112" x14ac:dyDescent="0.2">
+      <c r="A27" s="9" t="s">
         <v>672</v>
       </c>
-      <c r="B24" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C24" s="12" t="s">
+      <c r="B27" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C27" s="9" t="s">
         <v>680</v>
       </c>
-      <c r="D24" s="12" t="s">
+      <c r="D27" s="9" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A25" s="12" t="s">
+    <row r="28" spans="1:4" ht="126" x14ac:dyDescent="0.2">
+      <c r="A28" s="9" t="s">
         <v>672</v>
       </c>
-      <c r="B25" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C25" s="12" t="s">
+      <c r="B28" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C28" s="9" t="s">
         <v>681</v>
       </c>
-      <c r="D25" s="12" t="s">
+      <c r="D28" s="9" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="112" x14ac:dyDescent="0.2">
-      <c r="A26" s="12" t="s">
+    <row r="29" spans="1:4" ht="112" x14ac:dyDescent="0.2">
+      <c r="A29" s="9" t="s">
         <v>672</v>
       </c>
-      <c r="B26" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C26" s="12" t="s">
+      <c r="B29" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C29" s="9" t="s">
         <v>682</v>
       </c>
-      <c r="D26" s="12" t="s">
+      <c r="D29" s="9" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A27" s="12" t="s">
+    <row r="30" spans="1:4" ht="126" x14ac:dyDescent="0.2">
+      <c r="A30" s="9" t="s">
         <v>672</v>
       </c>
-      <c r="B27" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C27" s="12" t="s">
+      <c r="B30" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C30" s="9" t="s">
         <v>683</v>
       </c>
-      <c r="D27" s="12" t="s">
+      <c r="D30" s="9" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="84" x14ac:dyDescent="0.2">
-      <c r="A28" s="12" t="s">
+    <row r="31" spans="1:4" ht="84" x14ac:dyDescent="0.2">
+      <c r="A31" s="9" t="s">
         <v>672</v>
       </c>
-      <c r="B28" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C28" s="12" t="s">
+      <c r="B31" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C31" s="9" t="s">
         <v>684</v>
       </c>
-      <c r="D28" s="12" t="s">
+      <c r="D31" s="9" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A29" s="12" t="s">
+    <row r="32" spans="1:4" ht="126" x14ac:dyDescent="0.2">
+      <c r="A32" s="9" t="s">
         <v>672</v>
       </c>
-      <c r="B29" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C29" s="12" t="s">
+      <c r="B32" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C32" s="9" t="s">
         <v>685</v>
       </c>
-      <c r="D29" s="12" t="s">
+      <c r="D32" s="9" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A30" s="12" t="s">
+    <row r="33" spans="1:4" ht="126" x14ac:dyDescent="0.2">
+      <c r="A33" s="9" t="s">
         <v>672</v>
       </c>
-      <c r="B30" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C30" s="12" t="s">
+      <c r="B33" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C33" s="9" t="s">
         <v>686</v>
       </c>
-      <c r="D30" s="12" t="s">
+      <c r="D33" s="9" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A31" s="12" t="s">
+    <row r="34" spans="1:4" ht="126" x14ac:dyDescent="0.2">
+      <c r="A34" s="9" t="s">
         <v>672</v>
       </c>
-      <c r="B31" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C31" s="12" t="s">
+      <c r="B34" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C34" s="9" t="s">
         <v>687</v>
       </c>
-      <c r="D31" s="12" t="s">
+      <c r="D34" s="9" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A32" s="12" t="s">
+    <row r="35" spans="1:4" ht="126" x14ac:dyDescent="0.2">
+      <c r="A35" s="9" t="s">
         <v>672</v>
       </c>
-      <c r="B32" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C32" s="12" t="s">
+      <c r="B35" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C35" s="9" t="s">
         <v>688</v>
       </c>
-      <c r="D32" s="12" t="s">
+      <c r="D35" s="9" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A33" s="12" t="s">
+    <row r="36" spans="1:4" ht="126" x14ac:dyDescent="0.2">
+      <c r="A36" s="9" t="s">
         <v>672</v>
       </c>
-      <c r="B33" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C33" s="12" t="s">
+      <c r="B36" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C36" s="9" t="s">
         <v>689</v>
       </c>
-      <c r="D33" s="12" t="s">
+      <c r="D36" s="9" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="112" x14ac:dyDescent="0.2">
-      <c r="A34" s="12" t="s">
+    <row r="37" spans="1:4" ht="112" x14ac:dyDescent="0.2">
+      <c r="A37" s="9" t="s">
         <v>672</v>
       </c>
-      <c r="B34" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C34" s="12" t="s">
+      <c r="B37" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C37" s="9" t="s">
         <v>690</v>
       </c>
-      <c r="D34" s="12" t="s">
+      <c r="D37" s="9" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A35" s="12" t="s">
+    <row r="38" spans="1:4" ht="126" x14ac:dyDescent="0.2">
+      <c r="A38" s="9" t="s">
         <v>672</v>
       </c>
-      <c r="B35" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C35" s="12" t="s">
+      <c r="B38" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C38" s="9" t="s">
         <v>691</v>
       </c>
-      <c r="D35" s="12" t="s">
+      <c r="D38" s="9" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A36" s="12" t="s">
+    <row r="39" spans="1:4" ht="126" x14ac:dyDescent="0.2">
+      <c r="A39" s="9" t="s">
         <v>672</v>
       </c>
-      <c r="B36" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C36" s="12" t="s">
+      <c r="B39" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C39" s="9" t="s">
         <v>692</v>
       </c>
-      <c r="D36" s="12" t="s">
+      <c r="D39" s="9" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="84" x14ac:dyDescent="0.2">
-      <c r="A37" s="12" t="s">
+    <row r="40" spans="1:4" ht="84" x14ac:dyDescent="0.2">
+      <c r="A40" s="9" t="s">
         <v>672</v>
       </c>
-      <c r="B37" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C37" s="12" t="s">
+      <c r="B40" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C40" s="9" t="s">
         <v>693</v>
       </c>
-      <c r="D37" s="12" t="s">
+      <c r="D40" s="9" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="112" x14ac:dyDescent="0.2">
-      <c r="A38" s="12" t="s">
+    <row r="41" spans="1:4" ht="112" x14ac:dyDescent="0.2">
+      <c r="A41" s="9" t="s">
         <v>672</v>
       </c>
-      <c r="B38" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C38" s="12" t="s">
+      <c r="B41" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C41" s="9" t="s">
         <v>694</v>
       </c>
-      <c r="D38" s="12" t="s">
+      <c r="D41" s="9" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A39" s="12" t="s">
+    <row r="42" spans="1:4" ht="112" x14ac:dyDescent="0.2">
+      <c r="A42" s="10" t="s">
+        <v>672</v>
+      </c>
+      <c r="B42" s="10" t="s">
+        <v>776</v>
+      </c>
+      <c r="C42" s="10" t="s">
+        <v>778</v>
+      </c>
+      <c r="D42" s="10" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="112" x14ac:dyDescent="0.2">
+      <c r="A43" s="10" t="s">
+        <v>672</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>776</v>
+      </c>
+      <c r="C43" s="10" t="s">
+        <v>779</v>
+      </c>
+      <c r="D43" s="10" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="126" x14ac:dyDescent="0.2">
+      <c r="A44" s="9" t="s">
+        <v>672</v>
+      </c>
+      <c r="B44" s="9" t="s">
+        <v>781</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>782</v>
+      </c>
+      <c r="D44" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="9" t="s">
         <v>695</v>
       </c>
-      <c r="B39" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C39" s="12" t="s">
+      <c r="B45" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C45" s="9" t="s">
         <v>696</v>
       </c>
-      <c r="D39" s="12" t="s">
+      <c r="D45" s="9" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="140" x14ac:dyDescent="0.2">
-      <c r="A40" s="12" t="s">
+    <row r="46" spans="1:4" ht="140" x14ac:dyDescent="0.2">
+      <c r="A46" s="9" t="s">
         <v>697</v>
       </c>
-      <c r="B40" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C40" s="12" t="s">
+      <c r="B46" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C46" s="9" t="s">
         <v>698</v>
       </c>
-      <c r="D40" s="12" t="s">
+      <c r="D46" s="9" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A41" s="12" t="s">
+    <row r="47" spans="1:4" ht="126" x14ac:dyDescent="0.2">
+      <c r="A47" s="9" t="s">
         <v>697</v>
       </c>
-      <c r="B41" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C41" s="12" t="s">
+      <c r="B47" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C47" s="9" t="s">
         <v>699</v>
       </c>
-      <c r="D41" s="12" t="s">
+      <c r="D47" s="9" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="112" x14ac:dyDescent="0.2">
-      <c r="A42" s="12" t="s">
+    <row r="48" spans="1:4" ht="112" x14ac:dyDescent="0.2">
+      <c r="A48" s="9" t="s">
         <v>700</v>
       </c>
-      <c r="B42" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C42" s="12" t="s">
+      <c r="B48" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C48" s="9" t="s">
         <v>701</v>
       </c>
-      <c r="D42" s="12" t="s">
+      <c r="D48" s="9" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A43" s="12" t="s">
+    <row r="49" spans="1:4" ht="126" x14ac:dyDescent="0.2">
+      <c r="A49" s="9" t="s">
         <v>700</v>
       </c>
-      <c r="B43" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C43" s="12" t="s">
+      <c r="B49" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C49" s="9" t="s">
         <v>702</v>
       </c>
-      <c r="D43" s="12" t="s">
+      <c r="D49" s="9" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="112" x14ac:dyDescent="0.2">
-      <c r="A44" s="12" t="s">
+    <row r="50" spans="1:4" ht="112" x14ac:dyDescent="0.2">
+      <c r="A50" s="9" t="s">
         <v>703</v>
       </c>
-      <c r="B44" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C44" s="12" t="s">
+      <c r="B50" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C50" s="9" t="s">
         <v>704</v>
       </c>
-      <c r="D44" s="12" t="s">
+      <c r="D50" s="9" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="84" x14ac:dyDescent="0.2">
-      <c r="A45" s="12" t="s">
+    <row r="51" spans="1:4" ht="84" x14ac:dyDescent="0.2">
+      <c r="A51" s="9" t="s">
         <v>705</v>
       </c>
-      <c r="B45" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C45" s="12" t="s">
+      <c r="B51" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C51" s="9" t="s">
         <v>706</v>
       </c>
-      <c r="D45" s="12" t="s">
+      <c r="D51" s="9" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A46" s="12" t="s">
+    <row r="52" spans="1:4" ht="126" x14ac:dyDescent="0.2">
+      <c r="A52" s="9" t="s">
         <v>705</v>
       </c>
-      <c r="B46" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C46" s="12" t="s">
+      <c r="B52" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C52" s="9" t="s">
         <v>707</v>
       </c>
-      <c r="D46" s="12" t="s">
+      <c r="D52" s="9" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A47" s="12" t="s">
+    <row r="53" spans="1:4" ht="126" x14ac:dyDescent="0.2">
+      <c r="A53" s="9" t="s">
         <v>705</v>
       </c>
-      <c r="B47" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C47" s="12" t="s">
+      <c r="B53" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C53" s="9" t="s">
         <v>708</v>
       </c>
-      <c r="D47" s="12" t="s">
+      <c r="D53" s="9" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="98" x14ac:dyDescent="0.2">
-      <c r="A48" s="12" t="s">
+    <row r="54" spans="1:4" ht="98" x14ac:dyDescent="0.2">
+      <c r="A54" s="9" t="s">
         <v>705</v>
       </c>
-      <c r="B48" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C48" s="12" t="s">
+      <c r="B54" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C54" s="9" t="s">
         <v>709</v>
       </c>
-      <c r="D48" s="12" t="s">
+      <c r="D54" s="9" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="140" x14ac:dyDescent="0.2">
-      <c r="A49" s="12" t="s">
+    <row r="55" spans="1:4" ht="140" x14ac:dyDescent="0.2">
+      <c r="A55" s="9" t="s">
         <v>710</v>
       </c>
-      <c r="B49" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C49" s="12" t="s">
+      <c r="B55" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C55" s="9" t="s">
         <v>711</v>
       </c>
-      <c r="D49" s="12" t="s">
+      <c r="D55" s="9" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="140" x14ac:dyDescent="0.2">
-      <c r="A50" s="12" t="s">
+    <row r="56" spans="1:4" ht="140" x14ac:dyDescent="0.2">
+      <c r="A56" s="9" t="s">
         <v>712</v>
       </c>
-      <c r="B50" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C50" s="12" t="s">
+      <c r="B56" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C56" s="9" t="s">
         <v>713</v>
       </c>
-      <c r="D50" s="12" t="s">
+      <c r="D56" s="9" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="140" x14ac:dyDescent="0.2">
-      <c r="A51" s="12" t="s">
+    <row r="57" spans="1:4" ht="140" x14ac:dyDescent="0.2">
+      <c r="A57" s="9" t="s">
         <v>712</v>
       </c>
-      <c r="B51" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C51" s="12" t="s">
+      <c r="B57" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C57" s="9" t="s">
         <v>714</v>
       </c>
-      <c r="D51" s="12" t="s">
+      <c r="D57" s="9" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="140" x14ac:dyDescent="0.2">
-      <c r="A52" s="12" t="s">
+    <row r="58" spans="1:4" ht="126" x14ac:dyDescent="0.2">
+      <c r="A58" s="9" t="s">
+        <v>783</v>
+      </c>
+      <c r="B58" s="9" t="s">
+        <v>781</v>
+      </c>
+      <c r="C58" s="9" t="s">
+        <v>784</v>
+      </c>
+      <c r="D58" s="9" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="140" x14ac:dyDescent="0.2">
+      <c r="A59" s="9" t="s">
         <v>715</v>
       </c>
-      <c r="B52" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C52" s="12" t="s">
+      <c r="B59" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C59" s="9" t="s">
         <v>716</v>
       </c>
-      <c r="D52" s="12" t="s">
+      <c r="D59" s="9" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="112" x14ac:dyDescent="0.2">
-      <c r="A53" s="12" t="s">
+    <row r="60" spans="1:4" ht="112" x14ac:dyDescent="0.2">
+      <c r="A60" s="9" t="s">
         <v>717</v>
       </c>
-      <c r="B53" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C53" s="12" t="s">
+      <c r="B60" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C60" s="9" t="s">
         <v>718</v>
       </c>
-      <c r="D53" s="12" t="s">
+      <c r="D60" s="9" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A54" s="12" t="s">
+    <row r="61" spans="1:4" ht="126" x14ac:dyDescent="0.2">
+      <c r="A61" s="9" t="s">
         <v>717</v>
       </c>
-      <c r="B54" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C54" s="12" t="s">
+      <c r="B61" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C61" s="9" t="s">
         <v>719</v>
       </c>
-      <c r="D54" s="12" t="s">
+      <c r="D61" s="9" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="112" x14ac:dyDescent="0.2">
-      <c r="A55" s="12" t="s">
+    <row r="62" spans="1:4" ht="112" x14ac:dyDescent="0.2">
+      <c r="A62" s="9" t="s">
         <v>717</v>
       </c>
-      <c r="B55" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C55" s="12" t="s">
+      <c r="B62" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C62" s="9" t="s">
         <v>720</v>
       </c>
-      <c r="D55" s="12" t="s">
+      <c r="D62" s="9" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A56" s="12" t="s">
+    <row r="63" spans="1:4" ht="126" x14ac:dyDescent="0.2">
+      <c r="A63" s="9" t="s">
         <v>717</v>
       </c>
-      <c r="B56" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C56" s="12" t="s">
+      <c r="B63" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C63" s="9" t="s">
         <v>721</v>
       </c>
-      <c r="D56" s="12" t="s">
+      <c r="D63" s="9" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="57" spans="1:4" ht="112" x14ac:dyDescent="0.2">
-      <c r="A57" s="12" t="s">
+    <row r="64" spans="1:4" ht="112" x14ac:dyDescent="0.2">
+      <c r="A64" s="9" t="s">
         <v>717</v>
       </c>
-      <c r="B57" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C57" s="12" t="s">
+      <c r="B64" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C64" s="9" t="s">
         <v>722</v>
       </c>
-      <c r="D57" s="12" t="s">
+      <c r="D64" s="9" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A58" s="12" t="s">
+    <row r="65" spans="1:4" ht="126" x14ac:dyDescent="0.2">
+      <c r="A65" s="9" t="s">
+        <v>785</v>
+      </c>
+      <c r="B65" s="9" t="s">
+        <v>781</v>
+      </c>
+      <c r="C65" s="9" t="s">
+        <v>786</v>
+      </c>
+      <c r="D65" s="9" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" ht="126" x14ac:dyDescent="0.2">
+      <c r="A66" s="9" t="s">
         <v>723</v>
       </c>
-      <c r="B58" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C58" s="12" t="s">
+      <c r="B66" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C66" s="9" t="s">
         <v>724</v>
       </c>
-      <c r="D58" s="12" t="s">
+      <c r="D66" s="9" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="112" x14ac:dyDescent="0.2">
-      <c r="A59" s="12" t="s">
+    <row r="67" spans="1:4" ht="112" x14ac:dyDescent="0.2">
+      <c r="A67" s="9" t="s">
         <v>723</v>
       </c>
-      <c r="B59" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C59" s="12" t="s">
+      <c r="B67" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C67" s="9" t="s">
         <v>725</v>
       </c>
-      <c r="D59" s="12" t="s">
+      <c r="D67" s="9" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="60" spans="1:4" ht="112" x14ac:dyDescent="0.2">
-      <c r="A60" s="12" t="s">
+    <row r="68" spans="1:4" ht="112" x14ac:dyDescent="0.2">
+      <c r="A68" s="9" t="s">
         <v>723</v>
       </c>
-      <c r="B60" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C60" s="12" t="s">
+      <c r="B68" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C68" s="9" t="s">
         <v>726</v>
       </c>
-      <c r="D60" s="12" t="s">
+      <c r="D68" s="9" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="61" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A61" s="12" t="s">
+    <row r="69" spans="1:4" ht="140" x14ac:dyDescent="0.2">
+      <c r="A69" s="9" t="s">
+        <v>763</v>
+      </c>
+      <c r="B69" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C69" s="9" t="s">
+        <v>764</v>
+      </c>
+      <c r="D69" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" ht="126" x14ac:dyDescent="0.2">
+      <c r="A70" s="9" t="s">
+        <v>765</v>
+      </c>
+      <c r="B70" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C70" s="9" t="s">
+        <v>766</v>
+      </c>
+      <c r="D70" s="9" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" ht="126" x14ac:dyDescent="0.2">
+      <c r="A71" s="9" t="s">
         <v>727</v>
       </c>
-      <c r="B61" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C61" s="12" t="s">
+      <c r="B71" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C71" s="9" t="s">
         <v>728</v>
       </c>
-      <c r="D61" s="12" t="s">
+      <c r="D71" s="9" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="62" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A62" s="12" t="s">
+    <row r="72" spans="1:4" ht="126" x14ac:dyDescent="0.2">
+      <c r="A72" s="9" t="s">
         <v>727</v>
       </c>
-      <c r="B62" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C62" s="12" t="s">
+      <c r="B72" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C72" s="9" t="s">
         <v>729</v>
       </c>
-      <c r="D62" s="12" t="s">
+      <c r="D72" s="9" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="63" spans="1:4" ht="112" x14ac:dyDescent="0.2">
-      <c r="A63" s="12" t="s">
+    <row r="73" spans="1:4" ht="112" x14ac:dyDescent="0.2">
+      <c r="A73" s="9" t="s">
         <v>727</v>
       </c>
-      <c r="B63" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C63" s="12" t="s">
+      <c r="B73" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C73" s="9" t="s">
         <v>730</v>
       </c>
-      <c r="D63" s="12" t="s">
+      <c r="D73" s="9" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="64" spans="1:4" ht="112" x14ac:dyDescent="0.2">
-      <c r="A64" s="12" t="s">
+    <row r="74" spans="1:4" ht="112" x14ac:dyDescent="0.2">
+      <c r="A74" s="9" t="s">
         <v>727</v>
       </c>
-      <c r="B64" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C64" s="12" t="s">
+      <c r="B74" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C74" s="9" t="s">
         <v>731</v>
       </c>
-      <c r="D64" s="12" t="s">
+      <c r="D74" s="9" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="65" spans="1:4" ht="84" x14ac:dyDescent="0.2">
-      <c r="A65" s="12" t="s">
+    <row r="75" spans="1:4" ht="126" x14ac:dyDescent="0.2">
+      <c r="A75" s="10" t="s">
+        <v>727</v>
+      </c>
+      <c r="B75" s="10" t="s">
+        <v>776</v>
+      </c>
+      <c r="C75" s="10" t="s">
+        <v>780</v>
+      </c>
+      <c r="D75" s="10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" ht="84" x14ac:dyDescent="0.2">
+      <c r="A76" s="9" t="s">
         <v>732</v>
       </c>
-      <c r="B65" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C65" s="12" t="s">
+      <c r="B76" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C76" s="9" t="s">
         <v>733</v>
       </c>
-      <c r="D65" s="12" t="s">
+      <c r="D76" s="9" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="66" spans="1:4" ht="140" x14ac:dyDescent="0.2">
-      <c r="A66" s="12" t="s">
+    <row r="77" spans="1:4" ht="140" x14ac:dyDescent="0.2">
+      <c r="A77" s="9" t="s">
         <v>734</v>
       </c>
-      <c r="B66" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C66" s="12" t="s">
+      <c r="B77" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C77" s="9" t="s">
         <v>735</v>
       </c>
-      <c r="D66" s="12" t="s">
+      <c r="D77" s="9" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="67" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A67" s="12" t="s">
+    <row r="78" spans="1:4" ht="126" x14ac:dyDescent="0.2">
+      <c r="A78" s="9" t="s">
+        <v>767</v>
+      </c>
+      <c r="B78" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C78" s="9" t="s">
+        <v>768</v>
+      </c>
+      <c r="D78" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" ht="112" x14ac:dyDescent="0.2">
+      <c r="A79" s="9" t="s">
+        <v>789</v>
+      </c>
+      <c r="B79" s="9" t="s">
+        <v>790</v>
+      </c>
+      <c r="C79" s="9" t="s">
+        <v>791</v>
+      </c>
+      <c r="D79" s="9" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" ht="126" x14ac:dyDescent="0.2">
+      <c r="A80" s="9" t="s">
         <v>736</v>
       </c>
-      <c r="B67" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C67" s="12" t="s">
+      <c r="B80" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C80" s="9" t="s">
         <v>737</v>
       </c>
-      <c r="D67" s="12" t="s">
+      <c r="D80" s="9" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="68" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A68" s="12" t="s">
+    <row r="81" spans="1:4" ht="126" x14ac:dyDescent="0.2">
+      <c r="A81" s="9" t="s">
         <v>738</v>
       </c>
-      <c r="B68" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C68" s="12" t="s">
+      <c r="B81" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C81" s="9" t="s">
         <v>739</v>
       </c>
-      <c r="D68" s="12" t="s">
+      <c r="D81" s="9" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="69" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A69" s="12" t="s">
+    <row r="82" spans="1:4" ht="126" x14ac:dyDescent="0.2">
+      <c r="A82" s="9" t="s">
         <v>740</v>
       </c>
-      <c r="B69" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C69" s="12" t="s">
+      <c r="B82" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C82" s="9" t="s">
         <v>741</v>
       </c>
-      <c r="D69" s="12" t="s">
+      <c r="D82" s="9" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="70" spans="1:4" ht="140" x14ac:dyDescent="0.2">
-      <c r="A70" s="12" t="s">
+    <row r="83" spans="1:4" ht="140" x14ac:dyDescent="0.2">
+      <c r="A83" s="9" t="s">
         <v>742</v>
       </c>
-      <c r="B70" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C70" s="12" t="s">
+      <c r="B83" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C83" s="9" t="s">
         <v>743</v>
       </c>
-      <c r="D70" s="12" t="s">
+      <c r="D83" s="9" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="71" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A71" s="12" t="s">
+    <row r="84" spans="1:4" ht="126" x14ac:dyDescent="0.2">
+      <c r="A84" s="9" t="s">
         <v>744</v>
       </c>
-      <c r="B71" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C71" s="12" t="s">
+      <c r="B84" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C84" s="9" t="s">
         <v>745</v>
       </c>
-      <c r="D71" s="12" t="s">
+      <c r="D84" s="9" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="72" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A72" s="12" t="s">
+    <row r="85" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A85" s="9" t="s">
+        <v>748</v>
+      </c>
+      <c r="B85" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C85" s="9" t="s">
+        <v>749</v>
+      </c>
+      <c r="D85" s="9" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" ht="126" x14ac:dyDescent="0.2">
+      <c r="A86" s="9" t="s">
         <v>746</v>
       </c>
-      <c r="B72" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C72" s="12" t="s">
+      <c r="B86" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C86" s="9" t="s">
         <v>747</v>
       </c>
-      <c r="D72" s="12" t="s">
+      <c r="D86" s="9" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="73" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A73" s="12" t="s">
-        <v>748</v>
-      </c>
-      <c r="B73" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C73" s="12" t="s">
-        <v>749</v>
-      </c>
-      <c r="D73" s="12" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A74" s="12" t="s">
+    <row r="87" spans="1:4" ht="126" x14ac:dyDescent="0.2">
+      <c r="A87" s="9" t="s">
         <v>750</v>
       </c>
-      <c r="B74" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C74" s="12" t="s">
+      <c r="B87" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C87" s="9" t="s">
         <v>751</v>
       </c>
-      <c r="D74" s="12" t="s">
+      <c r="D87" s="9" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="75" spans="1:4" ht="112" x14ac:dyDescent="0.2">
-      <c r="A75" s="12" t="s">
+    <row r="88" spans="1:4" ht="98" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A88" s="9" t="s">
+        <v>769</v>
+      </c>
+      <c r="B88" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C88" s="9" t="s">
+        <v>770</v>
+      </c>
+      <c r="D88" s="9" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" ht="84" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A89" s="9" t="s">
+        <v>771</v>
+      </c>
+      <c r="B89" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C89" s="9" t="s">
+        <v>772</v>
+      </c>
+      <c r="D89" s="9" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" ht="98" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="9" t="s">
+        <v>773</v>
+      </c>
+      <c r="B90" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C90" s="9" t="s">
+        <v>774</v>
+      </c>
+      <c r="D90" s="9" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" ht="112" x14ac:dyDescent="0.2">
+      <c r="A91" s="9" t="s">
         <v>752</v>
       </c>
-      <c r="B75" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C75" s="12" t="s">
+      <c r="B91" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C91" s="9" t="s">
         <v>753</v>
       </c>
-      <c r="D75" s="12" t="s">
+      <c r="D91" s="9" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="76" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A76" s="12" t="s">
+    <row r="92" spans="1:4" ht="126" x14ac:dyDescent="0.2">
+      <c r="A92" s="9" t="s">
         <v>754</v>
       </c>
-      <c r="B76" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C76" s="12" t="s">
+      <c r="B92" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C92" s="9" t="s">
         <v>755</v>
       </c>
-      <c r="D76" s="12" t="s">
+      <c r="D92" s="9" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="77" spans="1:4" ht="140" x14ac:dyDescent="0.2">
-      <c r="A77" s="12" t="s">
+    <row r="93" spans="1:4" ht="140" x14ac:dyDescent="0.2">
+      <c r="A93" s="9" t="s">
         <v>756</v>
       </c>
-      <c r="B77" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C77" s="12" t="s">
+      <c r="B93" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C93" s="9" t="s">
         <v>757</v>
       </c>
-      <c r="D77" s="12" t="s">
+      <c r="D93" s="9" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="78" spans="1:4" ht="140" x14ac:dyDescent="0.2">
-      <c r="A78" s="12" t="s">
+    <row r="94" spans="1:4" ht="140" x14ac:dyDescent="0.2">
+      <c r="A94" s="9" t="s">
         <v>758</v>
       </c>
-      <c r="B78" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C78" s="12" t="s">
+      <c r="B94" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C94" s="9" t="s">
         <v>759</v>
       </c>
-      <c r="D78" s="12" t="s">
+      <c r="D94" s="9" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="79" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A79" s="12" t="s">
+    <row r="95" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A95" s="9" t="s">
         <v>760</v>
       </c>
-      <c r="B79" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C79" s="12" t="s">
+      <c r="B95" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C95" s="9" t="s">
         <v>761</v>
       </c>
-      <c r="D79" s="12" t="s">
+      <c r="D95" s="9" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="80" spans="1:4" ht="112" x14ac:dyDescent="0.2">
-      <c r="A80" s="12" t="s">
+    <row r="96" spans="1:4" ht="112" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A96" s="9" t="s">
         <v>760</v>
       </c>
-      <c r="B80" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C80" s="12" t="s">
+      <c r="B96" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C96" s="9" t="s">
         <v>762</v>
       </c>
-      <c r="D80" s="12" t="s">
+      <c r="D96" s="9" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="81" spans="1:4" ht="140" x14ac:dyDescent="0.2">
-      <c r="A81" s="12" t="s">
-        <v>763</v>
-      </c>
-      <c r="B81" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C81" s="12" t="s">
-        <v>764</v>
-      </c>
-      <c r="D81" s="12" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A82" s="12" t="s">
-        <v>765</v>
-      </c>
-      <c r="B82" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C82" s="12" t="s">
-        <v>766</v>
-      </c>
-      <c r="D82" s="12" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A83" s="12" t="s">
-        <v>767</v>
-      </c>
-      <c r="B83" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C83" s="12" t="s">
-        <v>768</v>
-      </c>
-      <c r="D83" s="12" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" ht="98" x14ac:dyDescent="0.2">
-      <c r="A84" s="12" t="s">
-        <v>769</v>
-      </c>
-      <c r="B84" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C84" s="12" t="s">
-        <v>770</v>
-      </c>
-      <c r="D84" s="12" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" ht="84" x14ac:dyDescent="0.2">
-      <c r="A85" s="12" t="s">
-        <v>771</v>
-      </c>
-      <c r="B85" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C85" s="12" t="s">
-        <v>772</v>
-      </c>
-      <c r="D85" s="12" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" ht="98" x14ac:dyDescent="0.2">
-      <c r="A86" s="12" t="s">
-        <v>773</v>
-      </c>
-      <c r="B86" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="C86" s="12" t="s">
-        <v>774</v>
-      </c>
-      <c r="D86" s="12" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" ht="112" x14ac:dyDescent="0.2">
-      <c r="A87" s="13" t="s">
-        <v>775</v>
-      </c>
-      <c r="B87" s="13" t="s">
-        <v>776</v>
-      </c>
-      <c r="C87" s="13" t="s">
-        <v>777</v>
-      </c>
-      <c r="D87" s="13" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" ht="112" x14ac:dyDescent="0.2">
-      <c r="A88" s="13" t="s">
-        <v>672</v>
-      </c>
-      <c r="B88" s="13" t="s">
-        <v>776</v>
-      </c>
-      <c r="C88" s="13" t="s">
-        <v>778</v>
-      </c>
-      <c r="D88" s="13" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4" ht="112" x14ac:dyDescent="0.2">
-      <c r="A89" s="13" t="s">
-        <v>672</v>
-      </c>
-      <c r="B89" s="13" t="s">
-        <v>776</v>
-      </c>
-      <c r="C89" s="13" t="s">
-        <v>779</v>
-      </c>
-      <c r="D89" s="13" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A90" s="13" t="s">
-        <v>727</v>
-      </c>
-      <c r="B90" s="13" t="s">
-        <v>776</v>
-      </c>
-      <c r="C90" s="13" t="s">
-        <v>780</v>
-      </c>
-      <c r="D90" s="13" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A91" s="12" t="s">
-        <v>672</v>
-      </c>
-      <c r="B91" s="12" t="s">
-        <v>781</v>
-      </c>
-      <c r="C91" s="12" t="s">
-        <v>782</v>
-      </c>
-      <c r="D91" s="12" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A92" s="12" t="s">
-        <v>783</v>
-      </c>
-      <c r="B92" s="12" t="s">
-        <v>781</v>
-      </c>
-      <c r="C92" s="12" t="s">
-        <v>784</v>
-      </c>
-      <c r="D92" s="12" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A93" s="12" t="s">
-        <v>785</v>
-      </c>
-      <c r="B93" s="12" t="s">
-        <v>781</v>
-      </c>
-      <c r="C93" s="12" t="s">
-        <v>786</v>
-      </c>
-      <c r="D93" s="12" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" ht="112" x14ac:dyDescent="0.2">
-      <c r="A94" s="13" t="s">
-        <v>787</v>
-      </c>
-      <c r="B94" s="13" t="s">
-        <v>788</v>
-      </c>
-      <c r="C94" s="13"/>
-      <c r="D94" s="13" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" ht="112" x14ac:dyDescent="0.2">
-      <c r="A95" s="12" t="s">
-        <v>789</v>
-      </c>
-      <c r="B95" s="12" t="s">
-        <v>790</v>
-      </c>
-      <c r="C95" s="12" t="s">
-        <v>791</v>
-      </c>
-      <c r="D95" s="12" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" ht="112" x14ac:dyDescent="0.2">
-      <c r="A96" s="13" t="s">
-        <v>775</v>
-      </c>
-      <c r="B96" s="13" t="s">
-        <v>792</v>
-      </c>
-      <c r="C96" s="13" t="s">
-        <v>793</v>
-      </c>
-      <c r="D96" s="13" t="s">
-        <v>30</v>
-      </c>
-    </row>
   </sheetData>
+  <autoFilter ref="A1:D96" xr:uid="{9507E3AC-07A7-7A43-825A-CB56AF56021E}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Charity"/>
+        <filter val="Distributive Justice"/>
+        <filter val="Economic Equality"/>
+        <filter val="Egalitarian Equity"/>
+        <filter val="Egalitarianism - equal distribution of resources."/>
+        <filter val="Equalitarianism"/>
+        <filter val="Equality"/>
+        <filter val="Equality."/>
+        <filter val="Equitable Distribution"/>
+        <filter val="Equitable Distribution."/>
+        <filter val="Equity"/>
+        <filter val="Equity Norm - The principle of fairness and equality."/>
+        <filter val="Equity Principle"/>
+        <filter val="Equity."/>
+        <filter val="Ethical Egalitarianism, aiming for equal distribution"/>
+        <filter val="Fairness"/>
+        <filter val="Fairness (Equality)"/>
+        <filter val="Fairness and Equality"/>
+        <filter val="fairness in distribution to achieve balance."/>
+        <filter val="fairness."/>
+        <filter val="Fairness/Equality"/>
+        <filter val="Fairness/Equality."/>
+        <filter val="Fostering Equality"/>
+        <filter val="maximising fairness."/>
+        <filter val="Maximizing Equal Distribution"/>
+        <filter val="Maximizing Equality"/>
+        <filter val="Maximizing Equity"/>
+        <filter val="Maximizing overall well-being"/>
+        <filter val="Maximum Economic Equality"/>
+        <filter val="Maximum Equality"/>
+        <filter val="Minimizing inequality"/>
+        <filter val="Social Equality"/>
+        <filter val="Social Justice"/>
+        <filter val="Utilitarianism - maximizing total happiness."/>
+        <filter val="Utilitarianism, focused on maximizing total happiness"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:D97">
+    <sortCondition ref="A2:A97"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0700F54-0547-5A4F-A343-D6F4173ABBD3}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:D159"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="26.5" style="3" customWidth="1"/>
-    <col min="2" max="2" width="28.83203125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="43.83203125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="43.5" style="3" customWidth="1"/>
+    <col min="1" max="1" width="26.5" style="2" customWidth="1"/>
+    <col min="2" max="2" width="28.83203125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="43.83203125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="43.5" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="13" t="s">
         <v>327</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="13" t="s">
         <v>328</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="13" t="s">
         <v>329</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="13" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="112" x14ac:dyDescent="0.2">
-      <c r="A2" s="14" t="s">
+    <row r="2" spans="1:4" ht="112" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="11" t="s">
         <v>331</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="11" t="s">
         <v>332</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="11" t="s">
         <v>333</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="D2" s="11" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="140" x14ac:dyDescent="0.2">
-      <c r="A3" s="14" t="s">
+    <row r="3" spans="1:4" ht="140" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="11" t="s">
         <v>334</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="11" t="s">
         <v>332</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="11" t="s">
         <v>335</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="11" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="140" x14ac:dyDescent="0.2">
-      <c r="A4" s="14" t="s">
+    <row r="4" spans="1:4" ht="140" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="11" t="s">
         <v>336</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="11" t="s">
         <v>332</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="11" t="s">
         <v>337</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="11" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="112" x14ac:dyDescent="0.2">
-      <c r="A5" s="14" t="s">
+    <row r="5" spans="1:4" ht="112" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="11" t="s">
         <v>336</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="11" t="s">
         <v>332</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="11" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="140" x14ac:dyDescent="0.2">
-      <c r="A6" s="14" t="s">
+    <row r="6" spans="1:4" ht="140" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="11" t="s">
         <v>339</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="11" t="s">
         <v>332</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="11" t="s">
         <v>340</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="11" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="140" x14ac:dyDescent="0.2">
-      <c r="A7" s="14" t="s">
+    <row r="7" spans="1:4" ht="140" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="11" t="s">
         <v>339</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="11" t="s">
         <v>332</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="11" t="s">
         <v>341</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="D7" s="11" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A8" s="14" t="s">
+    <row r="8" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="11" t="s">
         <v>339</v>
       </c>
-      <c r="B8" s="14" t="s">
+      <c r="B8" s="11" t="s">
         <v>332</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="C8" s="11" t="s">
         <v>342</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="D8" s="11" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="112" x14ac:dyDescent="0.2">
-      <c r="A9" s="14" t="s">
+    <row r="9" spans="1:4" ht="112" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="11" t="s">
         <v>343</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="11" t="s">
         <v>332</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="C9" s="11" t="s">
         <v>344</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="D9" s="11" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A10" s="14" t="s">
+    <row r="10" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="11" t="s">
         <v>345</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="B10" s="11" t="s">
         <v>332</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C10" s="11" t="s">
         <v>346</v>
       </c>
-      <c r="D10" s="14" t="s">
+      <c r="D10" s="11" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="140" x14ac:dyDescent="0.2">
-      <c r="A11" s="14" t="s">
+    <row r="11" spans="1:4" ht="140" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="11" t="s">
         <v>347</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="B11" s="11" t="s">
         <v>332</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="C11" s="11" t="s">
         <v>348</v>
       </c>
-      <c r="D11" s="14" t="s">
+      <c r="D11" s="11" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="140" x14ac:dyDescent="0.2">
-      <c r="A12" s="14" t="s">
+    <row r="12" spans="1:4" ht="140" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="B12" s="14" t="s">
+      <c r="B12" s="11" t="s">
         <v>332</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="C12" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="D12" s="14" t="s">
+      <c r="D12" s="11" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A13" s="14" t="s">
+    <row r="13" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="B13" s="14" t="s">
+      <c r="B13" s="11" t="s">
         <v>332</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="11" t="s">
         <v>351</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="D13" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="112" x14ac:dyDescent="0.2">
-      <c r="A14" s="14" t="s">
+    <row r="14" spans="1:4" ht="112" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="11" t="s">
         <v>332</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="C14" s="11" t="s">
         <v>352</v>
       </c>
-      <c r="D14" s="14" t="s">
+      <c r="D14" s="11" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A15" s="14" t="s">
+    <row r="15" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="B15" s="14" t="s">
+      <c r="B15" s="11" t="s">
         <v>332</v>
       </c>
-      <c r="C15" s="14" t="s">
+      <c r="C15" s="11" t="s">
         <v>353</v>
       </c>
-      <c r="D15" s="14" t="s">
+      <c r="D15" s="11" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A16" s="14" t="s">
+    <row r="16" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="B16" s="14" t="s">
+      <c r="B16" s="11" t="s">
         <v>332</v>
       </c>
-      <c r="C16" s="14" t="s">
+      <c r="C16" s="11" t="s">
         <v>354</v>
       </c>
-      <c r="D16" s="14" t="s">
+      <c r="D16" s="11" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="112" x14ac:dyDescent="0.2">
-      <c r="A17" s="14" t="s">
+    <row r="17" spans="1:4" ht="112" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="B17" s="14" t="s">
+      <c r="B17" s="11" t="s">
         <v>332</v>
       </c>
-      <c r="C17" s="14" t="s">
+      <c r="C17" s="11" t="s">
         <v>355</v>
       </c>
-      <c r="D17" s="14" t="s">
+      <c r="D17" s="11" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A18" s="14" t="s">
+    <row r="18" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="B18" s="14" t="s">
+      <c r="B18" s="11" t="s">
         <v>332</v>
       </c>
-      <c r="C18" s="14" t="s">
+      <c r="C18" s="11" t="s">
         <v>356</v>
       </c>
-      <c r="D18" s="14" t="s">
+      <c r="D18" s="11" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A19" s="14" t="s">
+    <row r="19" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="B19" s="14" t="s">
+      <c r="B19" s="11" t="s">
         <v>332</v>
       </c>
-      <c r="C19" s="14" t="s">
+      <c r="C19" s="11" t="s">
         <v>357</v>
       </c>
-      <c r="D19" s="14" t="s">
+      <c r="D19" s="11" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A20" s="14" t="s">
+    <row r="20" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="11" t="s">
         <v>358</v>
       </c>
-      <c r="B20" s="14" t="s">
+      <c r="B20" s="11" t="s">
         <v>332</v>
       </c>
-      <c r="C20" s="14" t="s">
+      <c r="C20" s="11" t="s">
         <v>359</v>
       </c>
-      <c r="D20" s="14" t="s">
+      <c r="D20" s="11" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="140" x14ac:dyDescent="0.2">
-      <c r="A21" s="15" t="s">
+    <row r="21" spans="1:4" ht="140" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="12" t="s">
         <v>360</v>
       </c>
-      <c r="B21" s="15" t="s">
+      <c r="B21" s="12" t="s">
         <v>361</v>
       </c>
-      <c r="C21" s="15" t="s">
+      <c r="C21" s="12" t="s">
         <v>362</v>
       </c>
-      <c r="D21" s="15" t="s">
+      <c r="D21" s="12" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A22" s="15" t="s">
+    <row r="22" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="12" t="s">
         <v>363</v>
       </c>
-      <c r="B22" s="15" t="s">
+      <c r="B22" s="12" t="s">
         <v>361</v>
       </c>
-      <c r="C22" s="15" t="s">
+      <c r="C22" s="12" t="s">
         <v>364</v>
       </c>
-      <c r="D22" s="15" t="s">
+      <c r="D22" s="12" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A23" s="15" t="s">
+    <row r="23" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="12" t="s">
         <v>336</v>
       </c>
-      <c r="B23" s="15" t="s">
+      <c r="B23" s="12" t="s">
         <v>361</v>
       </c>
-      <c r="C23" s="15" t="s">
+      <c r="C23" s="12" t="s">
         <v>365</v>
       </c>
-      <c r="D23" s="15" t="s">
+      <c r="D23" s="12" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A24" s="15" t="s">
+    <row r="24" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="12" t="s">
         <v>336</v>
       </c>
-      <c r="B24" s="15" t="s">
+      <c r="B24" s="12" t="s">
         <v>361</v>
       </c>
-      <c r="C24" s="15" t="s">
+      <c r="C24" s="12" t="s">
         <v>366</v>
       </c>
-      <c r="D24" s="15" t="s">
+      <c r="D24" s="12" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="112" x14ac:dyDescent="0.2">
-      <c r="A25" s="15" t="s">
+    <row r="25" spans="1:4" ht="112" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="12" t="s">
         <v>339</v>
       </c>
-      <c r="B25" s="15" t="s">
+      <c r="B25" s="12" t="s">
         <v>361</v>
       </c>
-      <c r="C25" s="15" t="s">
+      <c r="C25" s="12" t="s">
         <v>367</v>
       </c>
-      <c r="D25" s="15" t="s">
+      <c r="D25" s="12" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A26" s="15" t="s">
+    <row r="26" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="12" t="s">
         <v>339</v>
       </c>
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="12" t="s">
         <v>361</v>
       </c>
-      <c r="C26" s="15" t="s">
+      <c r="C26" s="12" t="s">
         <v>368</v>
       </c>
-      <c r="D26" s="15" t="s">
+      <c r="D26" s="12" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="112" x14ac:dyDescent="0.2">
-      <c r="A27" s="15" t="s">
+    <row r="27" spans="1:4" ht="112" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="12" t="s">
         <v>369</v>
       </c>
-      <c r="B27" s="15" t="s">
+      <c r="B27" s="12" t="s">
         <v>361</v>
       </c>
-      <c r="C27" s="15" t="s">
+      <c r="C27" s="12" t="s">
         <v>370</v>
       </c>
-      <c r="D27" s="15" t="s">
+      <c r="D27" s="12" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="140" x14ac:dyDescent="0.2">
-      <c r="A28" s="15" t="s">
+    <row r="28" spans="1:4" ht="140" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="12" t="s">
         <v>371</v>
       </c>
-      <c r="B28" s="15" t="s">
+      <c r="B28" s="12" t="s">
         <v>361</v>
       </c>
-      <c r="C28" s="15" t="s">
+      <c r="C28" s="12" t="s">
         <v>372</v>
       </c>
-      <c r="D28" s="15" t="s">
+      <c r="D28" s="12" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="140" x14ac:dyDescent="0.2">
-      <c r="A29" s="15" t="s">
+    <row r="29" spans="1:4" ht="140" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="12" t="s">
         <v>349</v>
       </c>
-      <c r="B29" s="15" t="s">
+      <c r="B29" s="12" t="s">
         <v>361</v>
       </c>
-      <c r="C29" s="15" t="s">
+      <c r="C29" s="12" t="s">
         <v>373</v>
       </c>
-      <c r="D29" s="15" t="s">
+      <c r="D29" s="12" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="112" x14ac:dyDescent="0.2">
-      <c r="A30" s="15" t="s">
+    <row r="30" spans="1:4" ht="112" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="12" t="s">
         <v>349</v>
       </c>
-      <c r="B30" s="15" t="s">
+      <c r="B30" s="12" t="s">
         <v>361</v>
       </c>
-      <c r="C30" s="15" t="s">
+      <c r="C30" s="12" t="s">
         <v>374</v>
       </c>
-      <c r="D30" s="15" t="s">
+      <c r="D30" s="12" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A31" s="15" t="s">
+    <row r="31" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="12" t="s">
         <v>349</v>
       </c>
-      <c r="B31" s="15" t="s">
+      <c r="B31" s="12" t="s">
         <v>361</v>
       </c>
-      <c r="C31" s="15" t="s">
+      <c r="C31" s="12" t="s">
         <v>375</v>
       </c>
-      <c r="D31" s="15" t="s">
+      <c r="D31" s="12" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="112" x14ac:dyDescent="0.2">
-      <c r="A32" s="15" t="s">
+    <row r="32" spans="1:4" ht="112" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="12" t="s">
         <v>376</v>
       </c>
-      <c r="B32" s="15" t="s">
+      <c r="B32" s="12" t="s">
         <v>361</v>
       </c>
-      <c r="C32" s="15" t="s">
+      <c r="C32" s="12" t="s">
         <v>377</v>
       </c>
-      <c r="D32" s="15" t="s">
+      <c r="D32" s="12" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="112" x14ac:dyDescent="0.2">
-      <c r="A33" s="14" t="s">
+    <row r="33" spans="1:4" ht="112" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="B33" s="14" t="s">
+      <c r="B33" s="11" t="s">
         <v>379</v>
       </c>
-      <c r="C33" s="14" t="s">
+      <c r="C33" s="11" t="s">
         <v>380</v>
       </c>
-      <c r="D33" s="14" t="s">
+      <c r="D33" s="11" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="112" x14ac:dyDescent="0.2">
-      <c r="A34" s="14" t="s">
+    <row r="34" spans="1:4" ht="112" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="11" t="s">
         <v>339</v>
       </c>
-      <c r="B34" s="14" t="s">
+      <c r="B34" s="11" t="s">
         <v>379</v>
       </c>
-      <c r="C34" s="14" t="s">
+      <c r="C34" s="11" t="s">
         <v>381</v>
       </c>
-      <c r="D34" s="14" t="s">
+      <c r="D34" s="11" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A35" s="14" t="s">
+    <row r="35" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="11" t="s">
         <v>382</v>
       </c>
-      <c r="B35" s="14" t="s">
+      <c r="B35" s="11" t="s">
         <v>379</v>
       </c>
-      <c r="C35" s="14" t="s">
+      <c r="C35" s="11" t="s">
         <v>383</v>
       </c>
-      <c r="D35" s="14" t="s">
+      <c r="D35" s="11" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="98" x14ac:dyDescent="0.2">
-      <c r="A36" s="14" t="s">
+    <row r="36" spans="1:4" ht="98" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="B36" s="14" t="s">
+      <c r="B36" s="11" t="s">
         <v>379</v>
       </c>
-      <c r="C36" s="14" t="s">
+      <c r="C36" s="11" t="s">
         <v>384</v>
       </c>
-      <c r="D36" s="14" t="s">
+      <c r="D36" s="11" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="98" x14ac:dyDescent="0.2">
-      <c r="A37" s="14" t="s">
+    <row r="37" spans="1:4" ht="98" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="B37" s="14" t="s">
+      <c r="B37" s="11" t="s">
         <v>379</v>
       </c>
-      <c r="C37" s="14" t="s">
+      <c r="C37" s="11" t="s">
         <v>384</v>
       </c>
-      <c r="D37" s="14" t="s">
+      <c r="D37" s="11" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="112" x14ac:dyDescent="0.2">
-      <c r="A38" s="14" t="s">
+    <row r="38" spans="1:4" ht="112" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="B38" s="14" t="s">
+      <c r="B38" s="11" t="s">
         <v>379</v>
       </c>
-      <c r="C38" s="14" t="s">
+      <c r="C38" s="11" t="s">
         <v>385</v>
       </c>
-      <c r="D38" s="14" t="s">
+      <c r="D38" s="11" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="98" x14ac:dyDescent="0.2">
-      <c r="A39" s="14" t="s">
+    <row r="39" spans="1:4" ht="98" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="B39" s="14" t="s">
+      <c r="B39" s="11" t="s">
         <v>379</v>
       </c>
-      <c r="C39" s="14" t="s">
+      <c r="C39" s="11" t="s">
         <v>386</v>
       </c>
-      <c r="D39" s="14" t="s">
+      <c r="D39" s="11" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="112" x14ac:dyDescent="0.2">
-      <c r="A40" s="14" t="s">
+    <row r="40" spans="1:4" ht="112" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="11" t="s">
         <v>376</v>
       </c>
-      <c r="B40" s="14" t="s">
+      <c r="B40" s="11" t="s">
         <v>379</v>
       </c>
-      <c r="C40" s="14" t="s">
+      <c r="C40" s="11" t="s">
         <v>387</v>
       </c>
-      <c r="D40" s="14" t="s">
+      <c r="D40" s="11" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A41" s="14" t="s">
+      <c r="A41" s="11" t="s">
         <v>388</v>
       </c>
-      <c r="B41" s="14" t="s">
+      <c r="B41" s="11" t="s">
         <v>379</v>
       </c>
-      <c r="C41" s="14" t="s">
+      <c r="C41" s="11" t="s">
         <v>389</v>
       </c>
-      <c r="D41" s="14" t="s">
+      <c r="D41" s="11" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A42" s="15" t="s">
+    <row r="42" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="12" t="s">
         <v>390</v>
       </c>
-      <c r="B42" s="15" t="s">
+      <c r="B42" s="12" t="s">
         <v>391</v>
       </c>
-      <c r="C42" s="15" t="s">
+      <c r="C42" s="12" t="s">
         <v>392</v>
       </c>
-      <c r="D42" s="15" t="s">
+      <c r="D42" s="12" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A43" s="15" t="s">
+    <row r="43" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="12" t="s">
         <v>393</v>
       </c>
-      <c r="B43" s="15" t="s">
+      <c r="B43" s="12" t="s">
         <v>391</v>
       </c>
-      <c r="C43" s="15" t="s">
+      <c r="C43" s="12" t="s">
         <v>394</v>
       </c>
-      <c r="D43" s="15" t="s">
+      <c r="D43" s="12" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="140" x14ac:dyDescent="0.2">
-      <c r="A44" s="15" t="s">
+    <row r="44" spans="1:4" ht="140" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="12" t="s">
         <v>395</v>
       </c>
-      <c r="B44" s="15" t="s">
+      <c r="B44" s="12" t="s">
         <v>391</v>
       </c>
-      <c r="C44" s="15" t="s">
+      <c r="C44" s="12" t="s">
         <v>396</v>
       </c>
-      <c r="D44" s="15" t="s">
+      <c r="D44" s="12" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="112" x14ac:dyDescent="0.2">
-      <c r="A45" s="15" t="s">
+    <row r="45" spans="1:4" ht="112" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="12" t="s">
         <v>397</v>
       </c>
-      <c r="B45" s="15" t="s">
+      <c r="B45" s="12" t="s">
         <v>391</v>
       </c>
-      <c r="C45" s="15" t="s">
+      <c r="C45" s="12" t="s">
         <v>398</v>
       </c>
-      <c r="D45" s="15" t="s">
+      <c r="D45" s="12" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A46" s="15" t="s">
+    <row r="46" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="12" t="s">
         <v>339</v>
       </c>
-      <c r="B46" s="15" t="s">
+      <c r="B46" s="12" t="s">
         <v>391</v>
       </c>
-      <c r="C46" s="15" t="s">
+      <c r="C46" s="12" t="s">
         <v>399</v>
       </c>
-      <c r="D46" s="15" t="s">
+      <c r="D46" s="12" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="112" x14ac:dyDescent="0.2">
-      <c r="A47" s="15"/>
-      <c r="B47" s="15" t="s">
+    <row r="47" spans="1:4" ht="112" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="12"/>
+      <c r="B47" s="12" t="s">
         <v>391</v>
       </c>
-      <c r="C47" s="15" t="s">
+      <c r="C47" s="12" t="s">
         <v>400</v>
       </c>
-      <c r="D47" s="15" t="s">
+      <c r="D47" s="12" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A48" s="14" t="s">
+    <row r="48" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="11" t="s">
         <v>331</v>
       </c>
-      <c r="B48" s="14" t="s">
+      <c r="B48" s="11" t="s">
         <v>401</v>
       </c>
-      <c r="C48" s="14" t="s">
+      <c r="C48" s="11" t="s">
         <v>402</v>
       </c>
-      <c r="D48" s="14" t="s">
+      <c r="D48" s="11" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="112" x14ac:dyDescent="0.2">
-      <c r="A49" s="14" t="s">
+    <row r="49" spans="1:4" ht="112" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="11" t="s">
         <v>403</v>
       </c>
-      <c r="B49" s="14" t="s">
+      <c r="B49" s="11" t="s">
         <v>401</v>
       </c>
-      <c r="C49" s="14" t="s">
+      <c r="C49" s="11" t="s">
         <v>404</v>
       </c>
-      <c r="D49" s="14" t="s">
+      <c r="D49" s="11" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A50" s="14" t="s">
+    <row r="50" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="B50" s="14" t="s">
+      <c r="B50" s="11" t="s">
         <v>401</v>
       </c>
-      <c r="C50" s="14" t="s">
+      <c r="C50" s="11" t="s">
         <v>405</v>
       </c>
-      <c r="D50" s="14" t="s">
+      <c r="D50" s="11" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="112" x14ac:dyDescent="0.2">
-      <c r="A51" s="14" t="s">
+    <row r="51" spans="1:4" ht="112" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="11" t="s">
         <v>406</v>
       </c>
-      <c r="B51" s="14" t="s">
+      <c r="B51" s="11" t="s">
         <v>401</v>
       </c>
-      <c r="C51" s="14" t="s">
+      <c r="C51" s="11" t="s">
         <v>407</v>
       </c>
-      <c r="D51" s="14" t="s">
+      <c r="D51" s="11" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="140" x14ac:dyDescent="0.2">
-      <c r="A52" s="15" t="s">
+      <c r="A52" s="14" t="s">
         <v>408</v>
       </c>
-      <c r="B52" s="15" t="s">
+      <c r="B52" s="14" t="s">
         <v>409</v>
       </c>
-      <c r="C52" s="15" t="s">
+      <c r="C52" s="14" t="s">
         <v>410</v>
       </c>
-      <c r="D52" s="15" t="s">
+      <c r="D52" s="14" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="140" x14ac:dyDescent="0.2">
-      <c r="A53" s="15" t="s">
+    <row r="53" spans="1:4" ht="140" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="12" t="s">
         <v>411</v>
       </c>
-      <c r="B53" s="15" t="s">
+      <c r="B53" s="12" t="s">
         <v>409</v>
       </c>
-      <c r="C53" s="15" t="s">
+      <c r="C53" s="12" t="s">
         <v>412</v>
       </c>
-      <c r="D53" s="15" t="s">
+      <c r="D53" s="12" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="140" x14ac:dyDescent="0.2">
-      <c r="A54" s="15" t="s">
+    <row r="54" spans="1:4" ht="140" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="12" t="s">
         <v>413</v>
       </c>
-      <c r="B54" s="15" t="s">
+      <c r="B54" s="12" t="s">
         <v>409</v>
       </c>
-      <c r="C54" s="15" t="s">
+      <c r="C54" s="12" t="s">
         <v>414</v>
       </c>
-      <c r="D54" s="15" t="s">
+      <c r="D54" s="12" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="112" x14ac:dyDescent="0.2">
-      <c r="A55" s="14" t="s">
+    <row r="55" spans="1:4" ht="112" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="11" t="s">
         <v>415</v>
       </c>
-      <c r="B55" s="14" t="s">
+      <c r="B55" s="11" t="s">
         <v>416</v>
       </c>
-      <c r="C55" s="14" t="s">
+      <c r="C55" s="11" t="s">
         <v>417</v>
       </c>
-      <c r="D55" s="14" t="s">
+      <c r="D55" s="11" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="112" x14ac:dyDescent="0.2">
-      <c r="A56" s="14" t="s">
+    <row r="56" spans="1:4" ht="112" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="11" t="s">
         <v>418</v>
       </c>
-      <c r="B56" s="14" t="s">
+      <c r="B56" s="11" t="s">
         <v>416</v>
       </c>
-      <c r="C56" s="14" t="s">
+      <c r="C56" s="11" t="s">
         <v>419</v>
       </c>
-      <c r="D56" s="14" t="s">
+      <c r="D56" s="11" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="57" spans="1:4" ht="112" x14ac:dyDescent="0.2">
-      <c r="A57" s="14" t="s">
+    <row r="57" spans="1:4" ht="112" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="B57" s="14" t="s">
+      <c r="B57" s="11" t="s">
         <v>416</v>
       </c>
-      <c r="C57" s="14" t="s">
+      <c r="C57" s="11" t="s">
         <v>420</v>
       </c>
-      <c r="D57" s="14" t="s">
+      <c r="D57" s="11" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="140" x14ac:dyDescent="0.2">
-      <c r="A58" s="15" t="s">
+    <row r="58" spans="1:4" ht="140" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="12" t="s">
         <v>421</v>
       </c>
-      <c r="B58" s="15" t="s">
+      <c r="B58" s="12" t="s">
         <v>422</v>
       </c>
-      <c r="C58" s="15" t="s">
+      <c r="C58" s="12" t="s">
         <v>423</v>
       </c>
-      <c r="D58" s="15" t="s">
+      <c r="D58" s="12" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A59" s="15" t="s">
+    <row r="59" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="12" t="s">
         <v>424</v>
       </c>
-      <c r="B59" s="15" t="s">
+      <c r="B59" s="12" t="s">
         <v>422</v>
       </c>
-      <c r="C59" s="15" t="s">
+      <c r="C59" s="12" t="s">
         <v>425</v>
       </c>
-      <c r="D59" s="15" t="s">
+      <c r="D59" s="12" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="60" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A60" s="15" t="s">
+    <row r="60" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="12" t="s">
         <v>426</v>
       </c>
-      <c r="B60" s="15" t="s">
+      <c r="B60" s="12" t="s">
         <v>422</v>
       </c>
-      <c r="C60" s="15" t="s">
+      <c r="C60" s="12" t="s">
         <v>427</v>
       </c>
-      <c r="D60" s="15" t="s">
+      <c r="D60" s="12" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="61" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A61" s="14" t="s">
+    <row r="61" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="11" t="s">
         <v>428</v>
       </c>
-      <c r="B61" s="14" t="s">
+      <c r="B61" s="11" t="s">
         <v>429</v>
       </c>
-      <c r="C61" s="14" t="s">
+      <c r="C61" s="11" t="s">
         <v>430</v>
       </c>
-      <c r="D61" s="14" t="s">
+      <c r="D61" s="11" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="62" spans="1:4" ht="140" x14ac:dyDescent="0.2">
-      <c r="A62" s="14" t="s">
+    <row r="62" spans="1:4" ht="140" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="11" t="s">
         <v>339</v>
       </c>
-      <c r="B62" s="14" t="s">
+      <c r="B62" s="11" t="s">
         <v>429</v>
       </c>
-      <c r="C62" s="14" t="s">
+      <c r="C62" s="11" t="s">
         <v>431</v>
       </c>
-      <c r="D62" s="14" t="s">
+      <c r="D62" s="11" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="63" spans="1:4" ht="140" x14ac:dyDescent="0.2">
-      <c r="A63" s="15" t="s">
+    <row r="63" spans="1:4" ht="140" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="12" t="s">
         <v>421</v>
       </c>
-      <c r="B63" s="15" t="s">
+      <c r="B63" s="12" t="s">
         <v>432</v>
       </c>
-      <c r="C63" s="15" t="s">
+      <c r="C63" s="12" t="s">
         <v>433</v>
       </c>
-      <c r="D63" s="15" t="s">
+      <c r="D63" s="12" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="64" spans="1:4" ht="140" x14ac:dyDescent="0.2">
-      <c r="A64" s="15" t="s">
+    <row r="64" spans="1:4" ht="140" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="12" t="s">
         <v>434</v>
       </c>
-      <c r="B64" s="15" t="s">
+      <c r="B64" s="12" t="s">
         <v>432</v>
       </c>
-      <c r="C64" s="15" t="s">
+      <c r="C64" s="12" t="s">
         <v>435</v>
       </c>
-      <c r="D64" s="15" t="s">
+      <c r="D64" s="12" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="65" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A65" s="14" t="s">
+    <row r="65" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="11" t="s">
         <v>382</v>
       </c>
-      <c r="B65" s="14" t="s">
+      <c r="B65" s="11" t="s">
         <v>436</v>
       </c>
-      <c r="C65" s="14" t="s">
+      <c r="C65" s="11" t="s">
         <v>437</v>
       </c>
-      <c r="D65" s="14" t="s">
+      <c r="D65" s="11" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="66" spans="1:4" ht="140" x14ac:dyDescent="0.2">
-      <c r="A66" s="14" t="s">
+    <row r="66" spans="1:4" ht="140" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="B66" s="14" t="s">
+      <c r="B66" s="11" t="s">
         <v>436</v>
       </c>
-      <c r="C66" s="14" t="s">
+      <c r="C66" s="11" t="s">
         <v>438</v>
       </c>
-      <c r="D66" s="14" t="s">
+      <c r="D66" s="11" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="67" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A67" s="15" t="s">
+    <row r="67" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="12" t="s">
         <v>369</v>
       </c>
-      <c r="B67" s="15" t="s">
+      <c r="B67" s="12" t="s">
         <v>439</v>
       </c>
-      <c r="C67" s="15" t="s">
+      <c r="C67" s="12" t="s">
         <v>440</v>
       </c>
-      <c r="D67" s="15" t="s">
+      <c r="D67" s="12" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="68" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A68" s="15" t="s">
+    <row r="68" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="12" t="s">
         <v>349</v>
       </c>
-      <c r="B68" s="15" t="s">
+      <c r="B68" s="12" t="s">
         <v>439</v>
       </c>
-      <c r="C68" s="15" t="s">
+      <c r="C68" s="12" t="s">
         <v>441</v>
       </c>
-      <c r="D68" s="15" t="s">
+      <c r="D68" s="12" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="69" spans="1:4" ht="140" x14ac:dyDescent="0.2">
-      <c r="A69" s="14" t="s">
+    <row r="69" spans="1:4" ht="140" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="11" t="s">
         <v>442</v>
       </c>
-      <c r="B69" s="14" t="s">
+      <c r="B69" s="11" t="s">
         <v>443</v>
       </c>
-      <c r="C69" s="14" t="s">
+      <c r="C69" s="11" t="s">
         <v>444</v>
       </c>
-      <c r="D69" s="14" t="s">
+      <c r="D69" s="11" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="70" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A70" s="14" t="s">
+    <row r="70" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="B70" s="14" t="s">
+      <c r="B70" s="11" t="s">
         <v>443</v>
       </c>
-      <c r="C70" s="14" t="s">
+      <c r="C70" s="11" t="s">
         <v>445</v>
       </c>
-      <c r="D70" s="14" t="s">
+      <c r="D70" s="11" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="71" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A71" s="15" t="s">
+    <row r="71" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="12" t="s">
         <v>339</v>
       </c>
-      <c r="B71" s="15" t="s">
+      <c r="B71" s="12" t="s">
         <v>446</v>
       </c>
-      <c r="C71" s="15" t="s">
+      <c r="C71" s="12" t="s">
         <v>447</v>
       </c>
-      <c r="D71" s="15" t="s">
+      <c r="D71" s="12" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="72" spans="1:4" ht="112" x14ac:dyDescent="0.2">
-      <c r="A72" s="15" t="s">
+    <row r="72" spans="1:4" ht="112" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="12" t="s">
         <v>339</v>
       </c>
-      <c r="B72" s="15" t="s">
+      <c r="B72" s="12" t="s">
         <v>446</v>
       </c>
-      <c r="C72" s="15" t="s">
+      <c r="C72" s="12" t="s">
         <v>448</v>
       </c>
-      <c r="D72" s="15" t="s">
+      <c r="D72" s="12" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A73" s="14" t="s">
+    <row r="73" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="B73" s="14" t="s">
+      <c r="B73" s="11" t="s">
         <v>449</v>
       </c>
-      <c r="C73" s="14" t="s">
+      <c r="C73" s="11" t="s">
         <v>450</v>
       </c>
-      <c r="D73" s="14" t="s">
+      <c r="D73" s="11" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="74" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A74" s="14" t="s">
+    <row r="74" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="B74" s="14" t="s">
+      <c r="B74" s="11" t="s">
         <v>449</v>
       </c>
-      <c r="C74" s="14" t="s">
+      <c r="C74" s="11" t="s">
         <v>451</v>
       </c>
-      <c r="D74" s="14" t="s">
+      <c r="D74" s="11" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="75" spans="1:4" ht="140" x14ac:dyDescent="0.2">
-      <c r="A75" s="15" t="s">
+    <row r="75" spans="1:4" ht="140" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="12" t="s">
         <v>452</v>
       </c>
-      <c r="B75" s="15" t="s">
+      <c r="B75" s="12" t="s">
         <v>453</v>
       </c>
-      <c r="C75" s="15" t="s">
+      <c r="C75" s="12" t="s">
         <v>454</v>
       </c>
-      <c r="D75" s="15" t="s">
+      <c r="D75" s="12" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="76" spans="1:4" ht="140" x14ac:dyDescent="0.2">
-      <c r="A76" s="14" t="s">
+    <row r="76" spans="1:4" ht="140" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="11" t="s">
         <v>455</v>
       </c>
-      <c r="B76" s="14" t="s">
+      <c r="B76" s="11" t="s">
         <v>456</v>
       </c>
-      <c r="C76" s="14" t="s">
+      <c r="C76" s="11" t="s">
         <v>457</v>
       </c>
-      <c r="D76" s="14" t="s">
+      <c r="D76" s="11" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="77" spans="1:4" ht="140" x14ac:dyDescent="0.2">
-      <c r="A77" s="15" t="s">
+    <row r="77" spans="1:4" ht="140" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A77" s="12" t="s">
         <v>458</v>
       </c>
-      <c r="B77" s="15" t="s">
+      <c r="B77" s="12" t="s">
         <v>459</v>
       </c>
-      <c r="C77" s="15" t="s">
+      <c r="C77" s="12" t="s">
         <v>460</v>
       </c>
-      <c r="D77" s="15" t="s">
+      <c r="D77" s="12" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="78" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A78" s="14" t="s">
+    <row r="78" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A78" s="11" t="s">
         <v>461</v>
       </c>
-      <c r="B78" s="14" t="s">
+      <c r="B78" s="11" t="s">
         <v>462</v>
       </c>
-      <c r="C78" s="14" t="s">
+      <c r="C78" s="11" t="s">
         <v>463</v>
       </c>
-      <c r="D78" s="14" t="s">
+      <c r="D78" s="11" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="79" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A79" s="15" t="s">
+    <row r="79" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="12" t="s">
         <v>464</v>
       </c>
-      <c r="B79" s="15" t="s">
+      <c r="B79" s="12" t="s">
         <v>465</v>
       </c>
-      <c r="C79" s="15" t="s">
+      <c r="C79" s="12" t="s">
         <v>466</v>
       </c>
-      <c r="D79" s="15" t="s">
+      <c r="D79" s="12" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="80" spans="1:4" ht="140" x14ac:dyDescent="0.2">
-      <c r="A80" s="14" t="s">
+    <row r="80" spans="1:4" ht="140" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A80" s="11" t="s">
         <v>467</v>
       </c>
-      <c r="B80" s="14" t="s">
+      <c r="B80" s="11" t="s">
         <v>468</v>
       </c>
-      <c r="C80" s="14" t="s">
+      <c r="C80" s="11" t="s">
         <v>469</v>
       </c>
-      <c r="D80" s="14" t="s">
+      <c r="D80" s="11" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="81" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A81" s="15" t="s">
+    <row r="81" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="12" t="s">
         <v>470</v>
       </c>
-      <c r="B81" s="15" t="s">
+      <c r="B81" s="12" t="s">
         <v>471</v>
       </c>
-      <c r="C81" s="15"/>
-      <c r="D81" s="15" t="s">
+      <c r="C81" s="12"/>
+      <c r="D81" s="12" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="82" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A82" s="14" t="s">
+    <row r="82" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A82" s="11" t="s">
         <v>363</v>
       </c>
-      <c r="B82" s="14" t="s">
+      <c r="B82" s="11" t="s">
         <v>472</v>
       </c>
-      <c r="C82" s="14" t="s">
+      <c r="C82" s="11" t="s">
         <v>473</v>
       </c>
-      <c r="D82" s="14" t="s">
+      <c r="D82" s="11" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="83" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A83" s="15" t="s">
+    <row r="83" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="12" t="s">
         <v>393</v>
       </c>
-      <c r="B83" s="15" t="s">
+      <c r="B83" s="12" t="s">
         <v>474</v>
       </c>
-      <c r="C83" s="15" t="s">
+      <c r="C83" s="12" t="s">
         <v>475</v>
       </c>
-      <c r="D83" s="15" t="s">
+      <c r="D83" s="12" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="84" spans="1:4" ht="98" x14ac:dyDescent="0.2">
-      <c r="A84" s="14" t="s">
+    <row r="84" spans="1:4" ht="98" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="11" t="s">
         <v>363</v>
       </c>
-      <c r="B84" s="14" t="s">
+      <c r="B84" s="11" t="s">
         <v>476</v>
       </c>
-      <c r="C84" s="14"/>
-      <c r="D84" s="14" t="s">
+      <c r="C84" s="11"/>
+      <c r="D84" s="11" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="85" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A85" s="15" t="s">
+    <row r="85" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A85" s="12" t="s">
         <v>363</v>
       </c>
-      <c r="B85" s="15" t="s">
+      <c r="B85" s="12" t="s">
         <v>477</v>
       </c>
-      <c r="C85" s="15" t="s">
+      <c r="C85" s="12" t="s">
         <v>478</v>
       </c>
-      <c r="D85" s="15" t="s">
+      <c r="D85" s="12" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="86" spans="1:4" ht="140" x14ac:dyDescent="0.2">
-      <c r="A86" s="14" t="s">
+    <row r="86" spans="1:4" ht="140" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="11" t="s">
         <v>363</v>
       </c>
-      <c r="B86" s="14" t="s">
+      <c r="B86" s="11" t="s">
         <v>479</v>
       </c>
-      <c r="C86" s="14" t="s">
+      <c r="C86" s="11" t="s">
         <v>480</v>
       </c>
-      <c r="D86" s="14" t="s">
+      <c r="D86" s="11" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="87" spans="1:4" ht="112" x14ac:dyDescent="0.2">
-      <c r="A87" s="15" t="s">
+    <row r="87" spans="1:4" ht="112" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A87" s="12" t="s">
         <v>382</v>
       </c>
-      <c r="B87" s="15" t="s">
+      <c r="B87" s="12" t="s">
         <v>481</v>
       </c>
-      <c r="C87" s="15" t="s">
+      <c r="C87" s="12" t="s">
         <v>482</v>
       </c>
-      <c r="D87" s="15" t="s">
+      <c r="D87" s="12" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="88" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A88" s="14" t="s">
+    <row r="88" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A88" s="11" t="s">
         <v>382</v>
       </c>
-      <c r="B88" s="14" t="s">
+      <c r="B88" s="11" t="s">
         <v>483</v>
       </c>
-      <c r="C88" s="14" t="s">
+      <c r="C88" s="11" t="s">
         <v>484</v>
       </c>
-      <c r="D88" s="14" t="s">
+      <c r="D88" s="11" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="89" spans="1:4" ht="140" x14ac:dyDescent="0.2">
-      <c r="A89" s="15" t="s">
+    <row r="89" spans="1:4" ht="140" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A89" s="12" t="s">
         <v>397</v>
       </c>
-      <c r="B89" s="15" t="s">
+      <c r="B89" s="12" t="s">
         <v>485</v>
       </c>
-      <c r="C89" s="15" t="s">
+      <c r="C89" s="12" t="s">
         <v>486</v>
       </c>
-      <c r="D89" s="15" t="s">
+      <c r="D89" s="12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="90" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A90" s="14" t="s">
+    <row r="90" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="11" t="s">
         <v>382</v>
       </c>
-      <c r="B90" s="14" t="s">
+      <c r="B90" s="11" t="s">
         <v>487</v>
       </c>
-      <c r="C90" s="14" t="s">
+      <c r="C90" s="11" t="s">
         <v>488</v>
       </c>
-      <c r="D90" s="14" t="s">
+      <c r="D90" s="11" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="91" spans="1:4" ht="112" x14ac:dyDescent="0.2">
-      <c r="A91" s="15" t="s">
+    <row r="91" spans="1:4" ht="112" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A91" s="12" t="s">
         <v>397</v>
       </c>
-      <c r="B91" s="15" t="s">
+      <c r="B91" s="12" t="s">
         <v>489</v>
       </c>
-      <c r="C91" s="15"/>
-      <c r="D91" s="15" t="s">
+      <c r="C91" s="12"/>
+      <c r="D91" s="12" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="92" spans="1:4" ht="140" x14ac:dyDescent="0.2">
-      <c r="A92" s="14" t="s">
+    <row r="92" spans="1:4" ht="140" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A92" s="11" t="s">
         <v>490</v>
       </c>
-      <c r="B92" s="14" t="s">
+      <c r="B92" s="11" t="s">
         <v>491</v>
       </c>
-      <c r="C92" s="14" t="s">
+      <c r="C92" s="11" t="s">
         <v>492</v>
       </c>
-      <c r="D92" s="14" t="s">
+      <c r="D92" s="11" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="93" spans="1:4" ht="140" x14ac:dyDescent="0.2">
-      <c r="A93" s="15" t="s">
+    <row r="93" spans="1:4" ht="140" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A93" s="12" t="s">
         <v>336</v>
       </c>
-      <c r="B93" s="15" t="s">
+      <c r="B93" s="12" t="s">
         <v>493</v>
       </c>
-      <c r="C93" s="15" t="s">
+      <c r="C93" s="12" t="s">
         <v>494</v>
       </c>
-      <c r="D93" s="15" t="s">
+      <c r="D93" s="12" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="94" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A94" s="14" t="s">
+    <row r="94" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="11" t="s">
         <v>495</v>
       </c>
-      <c r="B94" s="14" t="s">
+      <c r="B94" s="11" t="s">
         <v>496</v>
       </c>
-      <c r="C94" s="14" t="s">
+      <c r="C94" s="11" t="s">
         <v>497</v>
       </c>
-      <c r="D94" s="14" t="s">
+      <c r="D94" s="11" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="95" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A95" s="15" t="s">
+    <row r="95" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A95" s="12" t="s">
         <v>336</v>
       </c>
-      <c r="B95" s="15" t="s">
+      <c r="B95" s="12" t="s">
         <v>498</v>
       </c>
-      <c r="C95" s="15" t="s">
+      <c r="C95" s="12" t="s">
         <v>499</v>
       </c>
-      <c r="D95" s="15" t="s">
+      <c r="D95" s="12" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="96" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A96" s="14" t="s">
+    <row r="96" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A96" s="11" t="s">
         <v>369</v>
       </c>
-      <c r="B96" s="14" t="s">
+      <c r="B96" s="11" t="s">
         <v>500</v>
       </c>
-      <c r="C96" s="14" t="s">
+      <c r="C96" s="11" t="s">
         <v>501</v>
       </c>
-      <c r="D96" s="14" t="s">
+      <c r="D96" s="11" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="97" spans="1:4" ht="140" x14ac:dyDescent="0.2">
-      <c r="A97" s="15" t="s">
+    <row r="97" spans="1:4" ht="140" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A97" s="12" t="s">
         <v>502</v>
       </c>
-      <c r="B97" s="15" t="s">
+      <c r="B97" s="12" t="s">
         <v>503</v>
       </c>
-      <c r="C97" s="15" t="s">
+      <c r="C97" s="12" t="s">
         <v>504</v>
       </c>
-      <c r="D97" s="15" t="s">
+      <c r="D97" s="12" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="98" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A98" s="14" t="s">
+    <row r="98" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A98" s="11" t="s">
         <v>345</v>
       </c>
-      <c r="B98" s="14" t="s">
+      <c r="B98" s="11" t="s">
         <v>505</v>
       </c>
-      <c r="C98" s="14" t="s">
+      <c r="C98" s="11" t="s">
         <v>506</v>
       </c>
-      <c r="D98" s="14" t="s">
+      <c r="D98" s="11" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="99" spans="1:4" ht="140" x14ac:dyDescent="0.2">
-      <c r="A99" s="15" t="s">
+    <row r="99" spans="1:4" ht="140" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A99" s="12" t="s">
         <v>502</v>
       </c>
-      <c r="B99" s="15" t="s">
+      <c r="B99" s="12" t="s">
         <v>507</v>
       </c>
-      <c r="C99" s="15" t="s">
+      <c r="C99" s="12" t="s">
         <v>508</v>
       </c>
-      <c r="D99" s="15" t="s">
+      <c r="D99" s="12" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="100" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A100" s="17" t="s">
+    <row r="100" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A100" s="14" t="s">
         <v>345</v>
       </c>
-      <c r="B100" s="17" t="s">
+      <c r="B100" s="14" t="s">
         <v>509</v>
       </c>
-      <c r="C100" s="17" t="s">
+      <c r="C100" s="14" t="s">
         <v>510</v>
       </c>
-      <c r="D100" s="17" t="s">
+      <c r="D100" s="14" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="101" spans="1:4" ht="140" x14ac:dyDescent="0.2">
-      <c r="A101" s="15" t="s">
+    <row r="101" spans="1:4" ht="140" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A101" s="12" t="s">
         <v>345</v>
       </c>
-      <c r="B101" s="15" t="s">
+      <c r="B101" s="12" t="s">
         <v>511</v>
       </c>
-      <c r="C101" s="15" t="s">
+      <c r="C101" s="12" t="s">
         <v>512</v>
       </c>
-      <c r="D101" s="15" t="s">
+      <c r="D101" s="12" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="102" spans="1:4" ht="140" x14ac:dyDescent="0.2">
-      <c r="A102" s="14" t="s">
+    <row r="102" spans="1:4" ht="140" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A102" s="11" t="s">
         <v>513</v>
       </c>
-      <c r="B102" s="14" t="s">
+      <c r="B102" s="11" t="s">
         <v>514</v>
       </c>
-      <c r="C102" s="14" t="s">
+      <c r="C102" s="11" t="s">
         <v>515</v>
       </c>
-      <c r="D102" s="14" t="s">
+      <c r="D102" s="11" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="103" spans="1:4" ht="168" x14ac:dyDescent="0.2">
-      <c r="A103" s="15" t="s">
+    <row r="103" spans="1:4" ht="168" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A103" s="12" t="s">
         <v>516</v>
       </c>
-      <c r="B103" s="15" t="s">
+      <c r="B103" s="12" t="s">
         <v>517</v>
       </c>
-      <c r="C103" s="15" t="s">
+      <c r="C103" s="12" t="s">
         <v>518</v>
       </c>
-      <c r="D103" s="15" t="s">
+      <c r="D103" s="12" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="104" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A104" s="14" t="s">
+    <row r="104" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A104" s="11" t="s">
         <v>519</v>
       </c>
-      <c r="B104" s="14" t="s">
+      <c r="B104" s="11" t="s">
         <v>520</v>
       </c>
-      <c r="C104" s="14" t="s">
+      <c r="C104" s="11" t="s">
         <v>521</v>
       </c>
-      <c r="D104" s="14" t="s">
+      <c r="D104" s="11" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="105" spans="1:4" ht="140" x14ac:dyDescent="0.2">
-      <c r="A105" s="15" t="s">
+    <row r="105" spans="1:4" ht="140" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A105" s="12" t="s">
         <v>522</v>
       </c>
-      <c r="B105" s="15" t="s">
+      <c r="B105" s="12" t="s">
         <v>523</v>
       </c>
-      <c r="C105" s="15" t="s">
+      <c r="C105" s="12" t="s">
         <v>524</v>
       </c>
-      <c r="D105" s="15" t="s">
+      <c r="D105" s="12" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="106" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A106" s="14" t="s">
+    <row r="106" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A106" s="11" t="s">
         <v>525</v>
       </c>
-      <c r="B106" s="14" t="s">
+      <c r="B106" s="11" t="s">
         <v>526</v>
       </c>
-      <c r="C106" s="14" t="s">
+      <c r="C106" s="11" t="s">
         <v>527</v>
       </c>
-      <c r="D106" s="14" t="s">
+      <c r="D106" s="11" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="107" spans="1:4" ht="140" x14ac:dyDescent="0.2">
-      <c r="A107" s="15" t="s">
+    <row r="107" spans="1:4" ht="140" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A107" s="12" t="s">
         <v>528</v>
       </c>
-      <c r="B107" s="15" t="s">
+      <c r="B107" s="12" t="s">
         <v>529</v>
       </c>
-      <c r="C107" s="15" t="s">
+      <c r="C107" s="12" t="s">
         <v>530</v>
       </c>
-      <c r="D107" s="15" t="s">
+      <c r="D107" s="12" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="108" spans="1:4" ht="140" x14ac:dyDescent="0.2">
-      <c r="A108" s="14" t="s">
+    <row r="108" spans="1:4" ht="140" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A108" s="11" t="s">
         <v>531</v>
       </c>
-      <c r="B108" s="14" t="s">
+      <c r="B108" s="11" t="s">
         <v>532</v>
       </c>
-      <c r="C108" s="14" t="s">
+      <c r="C108" s="11" t="s">
         <v>533</v>
       </c>
-      <c r="D108" s="14" t="s">
+      <c r="D108" s="11" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="109" spans="1:4" ht="140" x14ac:dyDescent="0.2">
-      <c r="A109" s="15" t="s">
+    <row r="109" spans="1:4" ht="140" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A109" s="12" t="s">
         <v>534</v>
       </c>
-      <c r="B109" s="15" t="s">
+      <c r="B109" s="12" t="s">
         <v>535</v>
       </c>
-      <c r="C109" s="15" t="s">
+      <c r="C109" s="12" t="s">
         <v>536</v>
       </c>
-      <c r="D109" s="15" t="s">
+      <c r="D109" s="12" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="110" spans="1:4" ht="168" x14ac:dyDescent="0.2">
-      <c r="A110" s="14" t="s">
+    <row r="110" spans="1:4" ht="168" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A110" s="11" t="s">
         <v>442</v>
       </c>
-      <c r="B110" s="14" t="s">
+      <c r="B110" s="11" t="s">
         <v>537</v>
       </c>
-      <c r="C110" s="14" t="s">
+      <c r="C110" s="11" t="s">
         <v>538</v>
       </c>
-      <c r="D110" s="14" t="s">
+      <c r="D110" s="11" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="111" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A111" s="15" t="s">
+    <row r="111" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A111" s="12" t="s">
         <v>539</v>
       </c>
-      <c r="B111" s="15" t="s">
+      <c r="B111" s="12" t="s">
         <v>540</v>
       </c>
-      <c r="C111" s="15" t="s">
+      <c r="C111" s="12" t="s">
         <v>541</v>
       </c>
-      <c r="D111" s="15" t="s">
+      <c r="D111" s="12" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="112" spans="1:4" ht="154" x14ac:dyDescent="0.2">
-      <c r="A112" s="14" t="s">
+    <row r="112" spans="1:4" ht="154" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A112" s="11" t="s">
         <v>542</v>
       </c>
-      <c r="B112" s="14" t="s">
+      <c r="B112" s="11" t="s">
         <v>543</v>
       </c>
-      <c r="C112" s="14" t="s">
+      <c r="C112" s="11" t="s">
         <v>544</v>
       </c>
-      <c r="D112" s="14" t="s">
+      <c r="D112" s="11" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="113" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A113" s="15" t="s">
+    <row r="113" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A113" s="12" t="s">
         <v>371</v>
       </c>
-      <c r="B113" s="15" t="s">
+      <c r="B113" s="12" t="s">
         <v>545</v>
       </c>
-      <c r="C113" s="15"/>
-      <c r="D113" s="15" t="s">
+      <c r="C113" s="12"/>
+      <c r="D113" s="12" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="114" spans="1:4" ht="154" x14ac:dyDescent="0.2">
-      <c r="A114" s="14" t="s">
+    <row r="114" spans="1:4" ht="154" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A114" s="11" t="s">
         <v>542</v>
       </c>
-      <c r="B114" s="14" t="s">
+      <c r="B114" s="11" t="s">
         <v>546</v>
       </c>
-      <c r="C114" s="14" t="s">
+      <c r="C114" s="11" t="s">
         <v>547</v>
       </c>
-      <c r="D114" s="14" t="s">
+      <c r="D114" s="11" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="115" spans="1:4" ht="112" x14ac:dyDescent="0.2">
-      <c r="A115" s="15" t="s">
+    <row r="115" spans="1:4" ht="112" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A115" s="12" t="s">
         <v>349</v>
       </c>
-      <c r="B115" s="15" t="s">
+      <c r="B115" s="12" t="s">
         <v>548</v>
       </c>
-      <c r="C115" s="15" t="s">
+      <c r="C115" s="12" t="s">
         <v>549</v>
       </c>
-      <c r="D115" s="15" t="s">
+      <c r="D115" s="12" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="116" spans="1:4" ht="112" x14ac:dyDescent="0.2">
-      <c r="A116" s="14" t="s">
+    <row r="116" spans="1:4" ht="112" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A116" s="11" t="s">
         <v>339</v>
       </c>
-      <c r="B116" s="14" t="s">
+      <c r="B116" s="11" t="s">
         <v>550</v>
       </c>
-      <c r="C116" s="14" t="s">
+      <c r="C116" s="11" t="s">
         <v>551</v>
       </c>
-      <c r="D116" s="14" t="s">
+      <c r="D116" s="11" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="117" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A117" s="15" t="s">
+    <row r="117" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A117" s="12" t="s">
         <v>349</v>
       </c>
-      <c r="B117" s="15" t="s">
+      <c r="B117" s="12" t="s">
         <v>552</v>
       </c>
-      <c r="C117" s="15" t="s">
+      <c r="C117" s="12" t="s">
         <v>553</v>
       </c>
-      <c r="D117" s="15" t="s">
+      <c r="D117" s="12" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="118" spans="1:4" ht="140" x14ac:dyDescent="0.2">
-      <c r="A118" s="14" t="s">
+    <row r="118" spans="1:4" ht="140" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A118" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="B118" s="14" t="s">
+      <c r="B118" s="11" t="s">
         <v>554</v>
       </c>
-      <c r="C118" s="14" t="s">
+      <c r="C118" s="11" t="s">
         <v>555</v>
       </c>
-      <c r="D118" s="14" t="s">
+      <c r="D118" s="11" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="119" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A119" s="15" t="s">
+    <row r="119" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A119" s="12" t="s">
         <v>349</v>
       </c>
-      <c r="B119" s="15" t="s">
+      <c r="B119" s="12" t="s">
         <v>556</v>
       </c>
-      <c r="C119" s="15" t="s">
+      <c r="C119" s="12" t="s">
         <v>557</v>
       </c>
-      <c r="D119" s="15" t="s">
+      <c r="D119" s="12" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="120" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A120" s="14" t="s">
+    <row r="120" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A120" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="B120" s="14" t="s">
+      <c r="B120" s="11" t="s">
         <v>558</v>
       </c>
-      <c r="C120" s="14" t="s">
+      <c r="C120" s="11" t="s">
         <v>559</v>
       </c>
-      <c r="D120" s="14" t="s">
+      <c r="D120" s="11" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="121" spans="1:4" ht="140" x14ac:dyDescent="0.2">
-      <c r="A121" s="15" t="s">
+    <row r="121" spans="1:4" ht="140" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A121" s="12" t="s">
         <v>339</v>
       </c>
-      <c r="B121" s="15" t="s">
+      <c r="B121" s="12" t="s">
         <v>560</v>
       </c>
-      <c r="C121" s="15" t="s">
+      <c r="C121" s="12" t="s">
         <v>561</v>
       </c>
-      <c r="D121" s="15" t="s">
+      <c r="D121" s="12" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="122" spans="1:4" ht="112" x14ac:dyDescent="0.2">
-      <c r="A122" s="14" t="s">
+    <row r="122" spans="1:4" ht="112" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A122" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="B122" s="14" t="s">
+      <c r="B122" s="11" t="s">
         <v>562</v>
       </c>
-      <c r="C122" s="14" t="s">
+      <c r="C122" s="11" t="s">
         <v>563</v>
       </c>
-      <c r="D122" s="14" t="s">
+      <c r="D122" s="11" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="123" spans="1:4" ht="98" x14ac:dyDescent="0.2">
-      <c r="A123" s="15" t="s">
+    <row r="123" spans="1:4" ht="98" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A123" s="12" t="s">
         <v>339</v>
       </c>
-      <c r="B123" s="15" t="s">
+      <c r="B123" s="12" t="s">
         <v>564</v>
       </c>
-      <c r="C123" s="15"/>
-      <c r="D123" s="15" t="s">
+      <c r="C123" s="12"/>
+      <c r="D123" s="12" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="124" spans="1:4" ht="98" x14ac:dyDescent="0.2">
-      <c r="A124" s="14" t="s">
+    <row r="124" spans="1:4" ht="98" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A124" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="B124" s="14" t="s">
+      <c r="B124" s="11" t="s">
         <v>565</v>
       </c>
-      <c r="C124" s="14"/>
-      <c r="D124" s="14" t="s">
+      <c r="C124" s="11"/>
+      <c r="D124" s="11" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="125" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A125" s="15" t="s">
+    <row r="125" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A125" s="12" t="s">
         <v>349</v>
       </c>
-      <c r="B125" s="15" t="s">
+      <c r="B125" s="12" t="s">
         <v>566</v>
       </c>
-      <c r="C125" s="15" t="s">
+      <c r="C125" s="12" t="s">
         <v>567</v>
       </c>
-      <c r="D125" s="15" t="s">
+      <c r="D125" s="12" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="126" spans="1:4" ht="140" x14ac:dyDescent="0.2">
-      <c r="A126" s="14" t="s">
+    <row r="126" spans="1:4" ht="140" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A126" s="11" t="s">
         <v>339</v>
       </c>
-      <c r="B126" s="14" t="s">
+      <c r="B126" s="11" t="s">
         <v>568</v>
       </c>
-      <c r="C126" s="14" t="s">
+      <c r="C126" s="11" t="s">
         <v>569</v>
       </c>
-      <c r="D126" s="14" t="s">
+      <c r="D126" s="11" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="127" spans="1:4" ht="112" x14ac:dyDescent="0.2">
-      <c r="A127" s="15" t="s">
+    <row r="127" spans="1:4" ht="112" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A127" s="12" t="s">
         <v>349</v>
       </c>
-      <c r="B127" s="15" t="s">
+      <c r="B127" s="12" t="s">
         <v>570</v>
       </c>
-      <c r="C127" s="15" t="s">
+      <c r="C127" s="12" t="s">
         <v>571</v>
       </c>
-      <c r="D127" s="15" t="s">
+      <c r="D127" s="12" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="128" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A128" s="14" t="s">
+    <row r="128" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A128" s="11" t="s">
         <v>339</v>
       </c>
-      <c r="B128" s="14" t="s">
+      <c r="B128" s="11" t="s">
         <v>572</v>
       </c>
-      <c r="C128" s="14" t="s">
+      <c r="C128" s="11" t="s">
         <v>573</v>
       </c>
-      <c r="D128" s="14" t="s">
+      <c r="D128" s="11" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="129" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A129" s="15" t="s">
+    <row r="129" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A129" s="12" t="s">
         <v>339</v>
       </c>
-      <c r="B129" s="15" t="s">
+      <c r="B129" s="12" t="s">
         <v>574</v>
       </c>
-      <c r="C129" s="15" t="s">
+      <c r="C129" s="12" t="s">
         <v>575</v>
       </c>
-      <c r="D129" s="15" t="s">
+      <c r="D129" s="12" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="130" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A130" s="14" t="s">
+    <row r="130" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A130" s="11" t="s">
         <v>339</v>
       </c>
-      <c r="B130" s="14" t="s">
+      <c r="B130" s="11" t="s">
         <v>576</v>
       </c>
-      <c r="C130" s="14" t="s">
+      <c r="C130" s="11" t="s">
         <v>577</v>
       </c>
-      <c r="D130" s="14" t="s">
+      <c r="D130" s="11" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="131" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A131" s="15" t="s">
+    <row r="131" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A131" s="12" t="s">
         <v>349</v>
       </c>
-      <c r="B131" s="15" t="s">
+      <c r="B131" s="12" t="s">
         <v>578</v>
       </c>
-      <c r="C131" s="15" t="s">
+      <c r="C131" s="12" t="s">
         <v>579</v>
       </c>
-      <c r="D131" s="15" t="s">
+      <c r="D131" s="12" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="132" spans="1:4" ht="140" x14ac:dyDescent="0.2">
-      <c r="A132" s="14" t="s">
+    <row r="132" spans="1:4" ht="140" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A132" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="B132" s="14" t="s">
+      <c r="B132" s="11" t="s">
         <v>580</v>
       </c>
-      <c r="C132" s="14" t="s">
+      <c r="C132" s="11" t="s">
         <v>581</v>
       </c>
-      <c r="D132" s="14" t="s">
+      <c r="D132" s="11" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="133" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A133" s="15" t="s">
+    <row r="133" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A133" s="12" t="s">
         <v>349</v>
       </c>
-      <c r="B133" s="15" t="s">
+      <c r="B133" s="12" t="s">
         <v>582</v>
       </c>
-      <c r="C133" s="15" t="s">
+      <c r="C133" s="12" t="s">
         <v>583</v>
       </c>
-      <c r="D133" s="15" t="s">
+      <c r="D133" s="12" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="134" spans="1:4" ht="112" x14ac:dyDescent="0.2">
-      <c r="A134" s="14" t="s">
+    <row r="134" spans="1:4" ht="112" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A134" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="B134" s="14" t="s">
+      <c r="B134" s="11" t="s">
         <v>584</v>
       </c>
-      <c r="C134" s="14" t="s">
+      <c r="C134" s="11" t="s">
         <v>585</v>
       </c>
-      <c r="D134" s="14" t="s">
+      <c r="D134" s="11" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="135" spans="1:4" ht="140" x14ac:dyDescent="0.2">
-      <c r="A135" s="15" t="s">
+    <row r="135" spans="1:4" ht="140" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A135" s="12" t="s">
         <v>349</v>
       </c>
-      <c r="B135" s="15" t="s">
+      <c r="B135" s="12" t="s">
         <v>586</v>
       </c>
-      <c r="C135" s="15" t="s">
+      <c r="C135" s="12" t="s">
         <v>587</v>
       </c>
-      <c r="D135" s="15" t="s">
+      <c r="D135" s="12" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="136" spans="1:4" ht="140" x14ac:dyDescent="0.2">
-      <c r="A136" s="14" t="s">
+    <row r="136" spans="1:4" ht="140" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A136" s="11" t="s">
         <v>339</v>
       </c>
-      <c r="B136" s="14" t="s">
+      <c r="B136" s="11" t="s">
         <v>588</v>
       </c>
-      <c r="C136" s="14" t="s">
+      <c r="C136" s="11" t="s">
         <v>589</v>
       </c>
-      <c r="D136" s="14" t="s">
+      <c r="D136" s="11" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="137" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A137" s="15" t="s">
+    <row r="137" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A137" s="12" t="s">
         <v>339</v>
       </c>
-      <c r="B137" s="15" t="s">
+      <c r="B137" s="12" t="s">
         <v>590</v>
       </c>
-      <c r="C137" s="15" t="s">
+      <c r="C137" s="12" t="s">
         <v>591</v>
       </c>
-      <c r="D137" s="15" t="s">
+      <c r="D137" s="12" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="138" spans="1:4" ht="140" x14ac:dyDescent="0.2">
-      <c r="A138" s="14" t="s">
+    <row r="138" spans="1:4" ht="140" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A138" s="11" t="s">
         <v>339</v>
       </c>
-      <c r="B138" s="14" t="s">
+      <c r="B138" s="11" t="s">
         <v>592</v>
       </c>
-      <c r="C138" s="14" t="s">
+      <c r="C138" s="11" t="s">
         <v>593</v>
       </c>
-      <c r="D138" s="14" t="s">
+      <c r="D138" s="11" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="139" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A139" s="15" t="s">
+    <row r="139" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A139" s="12" t="s">
         <v>339</v>
       </c>
-      <c r="B139" s="15" t="s">
+      <c r="B139" s="12" t="s">
         <v>594</v>
       </c>
-      <c r="C139" s="15"/>
-      <c r="D139" s="15" t="s">
+      <c r="C139" s="12"/>
+      <c r="D139" s="12" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="140" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A140" s="14" t="s">
+    <row r="140" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A140" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="B140" s="14" t="s">
+      <c r="B140" s="11" t="s">
         <v>595</v>
       </c>
-      <c r="C140" s="14" t="s">
+      <c r="C140" s="11" t="s">
         <v>596</v>
       </c>
-      <c r="D140" s="14" t="s">
+      <c r="D140" s="11" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="141" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A141" s="15" t="s">
+    <row r="141" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A141" s="12" t="s">
         <v>339</v>
       </c>
-      <c r="B141" s="15" t="s">
+      <c r="B141" s="12" t="s">
         <v>597</v>
       </c>
-      <c r="C141" s="15" t="s">
+      <c r="C141" s="12" t="s">
         <v>598</v>
       </c>
-      <c r="D141" s="15" t="s">
+      <c r="D141" s="12" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="142" spans="1:4" ht="140" x14ac:dyDescent="0.2">
-      <c r="A142" s="14" t="s">
+    <row r="142" spans="1:4" ht="140" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A142" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="B142" s="14" t="s">
+      <c r="B142" s="11" t="s">
         <v>599</v>
       </c>
-      <c r="C142" s="14" t="s">
+      <c r="C142" s="11" t="s">
         <v>600</v>
       </c>
-      <c r="D142" s="14" t="s">
+      <c r="D142" s="11" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="143" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A143" s="15" t="s">
+    <row r="143" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A143" s="12" t="s">
         <v>339</v>
       </c>
-      <c r="B143" s="15" t="s">
+      <c r="B143" s="12" t="s">
         <v>601</v>
       </c>
-      <c r="C143" s="15" t="s">
+      <c r="C143" s="12" t="s">
         <v>602</v>
       </c>
-      <c r="D143" s="15" t="s">
+      <c r="D143" s="12" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="144" spans="1:4" ht="112" x14ac:dyDescent="0.2">
-      <c r="A144" s="14" t="s">
+    <row r="144" spans="1:4" ht="112" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A144" s="11" t="s">
         <v>339</v>
       </c>
-      <c r="B144" s="14" t="s">
+      <c r="B144" s="11" t="s">
         <v>603</v>
       </c>
-      <c r="C144" s="14" t="s">
+      <c r="C144" s="11" t="s">
         <v>604</v>
       </c>
-      <c r="D144" s="14" t="s">
+      <c r="D144" s="11" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="145" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A145" s="15" t="s">
+    <row r="145" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A145" s="12" t="s">
         <v>339</v>
       </c>
-      <c r="B145" s="15" t="s">
+      <c r="B145" s="12" t="s">
         <v>605</v>
       </c>
-      <c r="C145" s="15" t="s">
+      <c r="C145" s="12" t="s">
         <v>606</v>
       </c>
-      <c r="D145" s="15" t="s">
+      <c r="D145" s="12" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="146" spans="1:4" ht="140" x14ac:dyDescent="0.2">
-      <c r="A146" s="14" t="s">
+    <row r="146" spans="1:4" ht="140" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A146" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="B146" s="14" t="s">
+      <c r="B146" s="11" t="s">
         <v>607</v>
       </c>
-      <c r="C146" s="14" t="s">
+      <c r="C146" s="11" t="s">
         <v>608</v>
       </c>
-      <c r="D146" s="14" t="s">
+      <c r="D146" s="11" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="147" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A147" s="15" t="s">
+    <row r="147" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A147" s="12" t="s">
         <v>406</v>
       </c>
-      <c r="B147" s="15" t="s">
+      <c r="B147" s="12" t="s">
         <v>609</v>
       </c>
-      <c r="C147" s="15" t="s">
+      <c r="C147" s="12" t="s">
         <v>610</v>
       </c>
-      <c r="D147" s="15" t="s">
+      <c r="D147" s="12" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="148" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A148" s="14" t="s">
+    <row r="148" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A148" s="11" t="s">
         <v>406</v>
       </c>
-      <c r="B148" s="14" t="s">
+      <c r="B148" s="11" t="s">
         <v>611</v>
       </c>
-      <c r="C148" s="14" t="s">
+      <c r="C148" s="11" t="s">
         <v>612</v>
       </c>
-      <c r="D148" s="14" t="s">
+      <c r="D148" s="11" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="149" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A149" s="15" t="s">
+    <row r="149" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A149" s="12" t="s">
         <v>406</v>
       </c>
-      <c r="B149" s="15" t="s">
+      <c r="B149" s="12" t="s">
         <v>613</v>
       </c>
-      <c r="C149" s="15" t="s">
+      <c r="C149" s="12" t="s">
         <v>614</v>
       </c>
-      <c r="D149" s="15" t="s">
+      <c r="D149" s="12" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="150" spans="1:4" ht="168" x14ac:dyDescent="0.2">
-      <c r="A150" s="14" t="s">
+    <row r="150" spans="1:4" ht="168" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A150" s="11" t="s">
         <v>615</v>
       </c>
-      <c r="B150" s="14" t="s">
+      <c r="B150" s="11" t="s">
         <v>616</v>
       </c>
-      <c r="C150" s="14" t="s">
+      <c r="C150" s="11" t="s">
         <v>617</v>
       </c>
-      <c r="D150" s="14" t="s">
+      <c r="D150" s="11" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="151" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A151" s="15" t="s">
+    <row r="151" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A151" s="12" t="s">
         <v>618</v>
       </c>
-      <c r="B151" s="15" t="s">
+      <c r="B151" s="12" t="s">
         <v>619</v>
       </c>
-      <c r="C151" s="15" t="s">
+      <c r="C151" s="12" t="s">
         <v>620</v>
       </c>
-      <c r="D151" s="15" t="s">
+      <c r="D151" s="12" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="152" spans="1:4" ht="140" x14ac:dyDescent="0.2">
-      <c r="A152" s="14" t="s">
+    <row r="152" spans="1:4" ht="140" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A152" s="11" t="s">
         <v>618</v>
       </c>
-      <c r="B152" s="14" t="s">
+      <c r="B152" s="11" t="s">
         <v>621</v>
       </c>
-      <c r="C152" s="14" t="s">
+      <c r="C152" s="11" t="s">
         <v>622</v>
       </c>
-      <c r="D152" s="14" t="s">
+      <c r="D152" s="11" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="153" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A153" s="15" t="s">
+    <row r="153" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A153" s="12" t="s">
         <v>623</v>
       </c>
-      <c r="B153" s="15" t="s">
+      <c r="B153" s="12" t="s">
         <v>624</v>
       </c>
-      <c r="C153" s="15" t="s">
+      <c r="C153" s="12" t="s">
         <v>625</v>
       </c>
-      <c r="D153" s="15" t="s">
+      <c r="D153" s="12" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="154" spans="1:4" ht="112" x14ac:dyDescent="0.2">
-      <c r="A154" s="14" t="s">
+    <row r="154" spans="1:4" ht="112" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A154" s="11" t="s">
         <v>626</v>
       </c>
-      <c r="B154" s="14" t="s">
+      <c r="B154" s="11" t="s">
         <v>627</v>
       </c>
-      <c r="C154" s="14" t="s">
+      <c r="C154" s="11" t="s">
         <v>628</v>
       </c>
-      <c r="D154" s="14" t="s">
+      <c r="D154" s="11" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:4" ht="140" x14ac:dyDescent="0.2">
-      <c r="A155" s="15" t="s">
+    <row r="155" spans="1:4" ht="140" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A155" s="12" t="s">
         <v>629</v>
       </c>
-      <c r="B155" s="15" t="s">
+      <c r="B155" s="12" t="s">
         <v>630</v>
       </c>
-      <c r="C155" s="15" t="s">
+      <c r="C155" s="12" t="s">
         <v>631</v>
       </c>
-      <c r="D155" s="15" t="s">
+      <c r="D155" s="12" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="156" spans="1:4" ht="154" x14ac:dyDescent="0.2">
-      <c r="A156" s="14" t="s">
+    <row r="156" spans="1:4" ht="154" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A156" s="11" t="s">
         <v>632</v>
       </c>
-      <c r="B156" s="14" t="s">
+      <c r="B156" s="11" t="s">
         <v>633</v>
       </c>
-      <c r="C156" s="14" t="s">
+      <c r="C156" s="11" t="s">
         <v>634</v>
       </c>
-      <c r="D156" s="14" t="s">
+      <c r="D156" s="11" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="157" spans="1:4" ht="98" x14ac:dyDescent="0.2">
-      <c r="A157" s="15" t="s">
+    <row r="157" spans="1:4" ht="98" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A157" s="12" t="s">
         <v>635</v>
       </c>
-      <c r="B157" s="15" t="s">
+      <c r="B157" s="12" t="s">
         <v>636</v>
       </c>
-      <c r="C157" s="15" t="s">
+      <c r="C157" s="12" t="s">
         <v>637</v>
       </c>
-      <c r="D157" s="15" t="s">
+      <c r="D157" s="12" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="158" spans="1:4" ht="140" x14ac:dyDescent="0.2">
-      <c r="A158" s="14" t="s">
+    <row r="158" spans="1:4" ht="140" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A158" s="11" t="s">
         <v>638</v>
       </c>
-      <c r="B158" s="14" t="s">
+      <c r="B158" s="11" t="s">
         <v>639</v>
       </c>
-      <c r="C158" s="14" t="s">
+      <c r="C158" s="11" t="s">
         <v>640</v>
       </c>
-      <c r="D158" s="14" t="s">
+      <c r="D158" s="11" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="159" spans="1:4" ht="126" x14ac:dyDescent="0.2">
-      <c r="A159" s="14" t="s">
+    <row r="159" spans="1:4" ht="126" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A159" s="11" t="s">
         <v>641</v>
       </c>
-      <c r="B159" s="14"/>
-      <c r="C159" s="14" t="s">
+      <c r="B159" s="11"/>
+      <c r="C159" s="11" t="s">
         <v>642</v>
       </c>
-      <c r="D159" s="14" t="s">
+      <c r="D159" s="11" t="s">
         <v>245</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:D159" xr:uid="{D0700F54-0547-5A4F-A343-D6F4173ABBD3}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Maintain Existing Wealth Disparity"/>
+        <filter val="Utility Maximization"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -7796,11 +7815,11 @@
   <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="54.1640625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="54.1640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="128" x14ac:dyDescent="0.2">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="8" t="s">
         <v>228</v>
       </c>
     </row>
@@ -7824,155 +7843,155 @@
   <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="48.1640625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="48.1640625" style="2" customWidth="1"/>
     <col min="3" max="3" width="53.83203125" customWidth="1"/>
     <col min="5" max="5" width="54.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="9" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:5" s="6" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A1" s="5" t="s">
         <v>324</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="6" t="s">
         <v>326</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="6" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="144" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>319</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="128" x14ac:dyDescent="0.2">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="3" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="128" x14ac:dyDescent="0.2">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="112" x14ac:dyDescent="0.2">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="144" x14ac:dyDescent="0.2">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="128" x14ac:dyDescent="0.2">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="128" x14ac:dyDescent="0.2">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="128" x14ac:dyDescent="0.2">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="144" x14ac:dyDescent="0.2">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="3" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="128" x14ac:dyDescent="0.2">
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="3" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="128" x14ac:dyDescent="0.2">
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="3" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="128" x14ac:dyDescent="0.2">
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="3" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="112" x14ac:dyDescent="0.2">
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="3" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="144" x14ac:dyDescent="0.2">
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="3" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="112" x14ac:dyDescent="0.2">
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="3" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="17" spans="3:3" ht="128" x14ac:dyDescent="0.2">
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="3" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="18" spans="3:3" ht="128" x14ac:dyDescent="0.2">
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="3" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="19" spans="3:3" ht="128" x14ac:dyDescent="0.2">
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="3" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="20" spans="3:3" ht="80" x14ac:dyDescent="0.2">
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="21" spans="3:3" ht="128" x14ac:dyDescent="0.2">
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="3" t="s">
         <v>6</v>
       </c>
     </row>

--- a/experiment/instructions/ai_query_11_classified.xlsx
+++ b/experiment/instructions/ai_query_11_classified.xlsx
@@ -1,26 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/elfre4573/Documents/GitHub/AI_advice/experiment/instructions/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0BDF674-1AB9-1243-88B0-9D62C319BCB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB1DAD38-CF68-9147-A0D8-696B8DB9DD18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17480" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17480" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="give 3" sheetId="2" r:id="rId1"/>
     <sheet name="give 3 - full sentence" sheetId="7" r:id="rId2"/>
-    <sheet name="give 0" sheetId="6" r:id="rId3"/>
-    <sheet name="take 4" sheetId="4" r:id="rId4"/>
-    <sheet name="others" sheetId="3" r:id="rId5"/>
+    <sheet name="Eleonora top choices" sheetId="8" r:id="rId3"/>
+    <sheet name="give 0" sheetId="6" r:id="rId4"/>
+    <sheet name="take 4" sheetId="4" r:id="rId5"/>
+    <sheet name="others" sheetId="3" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'give 0'!$A$1:$D$159</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'give 0'!$A$1:$D$159</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'give 3 - full sentence'!$A$1:$D$96</definedName>
   </definedNames>
   <calcPr calcId="0"/>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1182" uniqueCount="795">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1222" uniqueCount="795">
   <si>
     <t>Evaluative Standard: Ethical Egalitarianism, aiming for equal distribution
 Recommendation: The decision-maker should give $3 to the recipient. 
@@ -5578,6 +5579,162 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A2AC988-BEEA-9244-BA2F-7C0ABFE03798}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="17.5" customWidth="1"/>
+    <col min="2" max="2" width="21.83203125" customWidth="1"/>
+    <col min="3" max="3" width="21.5" customWidth="1"/>
+    <col min="4" max="4" width="31.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="A1" s="15" t="s">
+        <v>327</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>328</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>329</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="154" x14ac:dyDescent="0.2">
+      <c r="A2" s="9" t="s">
+        <v>672</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>679</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="126" x14ac:dyDescent="0.2">
+      <c r="A3" s="9" t="s">
+        <v>672</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>680</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="154" x14ac:dyDescent="0.2">
+      <c r="A4" s="9" t="s">
+        <v>712</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>713</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="140" x14ac:dyDescent="0.2">
+      <c r="A5" s="9" t="s">
+        <v>783</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>781</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>784</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="154" x14ac:dyDescent="0.2">
+      <c r="A6" s="9" t="s">
+        <v>717</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>719</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="126" x14ac:dyDescent="0.2">
+      <c r="A7" s="9" t="s">
+        <v>717</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>722</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="154" x14ac:dyDescent="0.2">
+      <c r="A8" s="9" t="s">
+        <v>723</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>724</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="140" x14ac:dyDescent="0.2">
+      <c r="A9" s="9" t="s">
+        <v>723</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>725</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="140" x14ac:dyDescent="0.2">
+      <c r="A10" s="9" t="s">
+        <v>727</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>729</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0700F54-0547-5A4F-A343-D6F4173ABBD3}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:D159"/>
@@ -7810,7 +7967,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{399103A6-82F6-5B41-8361-39C43BF895A7}">
   <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -7838,7 +7995,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F224ACC2-145B-384E-88BE-AC5A7C03AD84}">
   <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
